--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="0" windowWidth="24640" windowHeight="15000" tabRatio="684"/>
+    <workbookView xWindow="4580" yWindow="0" windowWidth="25840" windowHeight="22540" tabRatio="684" firstSheet="47" activeTab="51"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -56,9 +56,9 @@
     <sheet name="A26.sector.csv" sheetId="6" r:id="rId47"/>
     <sheet name="A26.subsector_logit.csv" sheetId="32" r:id="rId48"/>
     <sheet name="A26.subsector_shrwt.csv" sheetId="33" r:id="rId49"/>
-    <sheet name="A26_subsector_interp.csv" sheetId="51" r:id="rId50"/>
+    <sheet name="A26.subsector_interp.csv" sheetId="51" r:id="rId50"/>
     <sheet name="A26.globaltech_cost.csv" sheetId="31" r:id="rId51"/>
-    <sheet name="A26.globaltech_coef.csv" sheetId="7" r:id="rId52"/>
+    <sheet name="A26.globaltech_eff.csv" sheetId="7" r:id="rId52"/>
     <sheet name="A26.globaltech_shrwt.csv" sheetId="52" r:id="rId53"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="194">
   <si>
     <t>technology</t>
   </si>
@@ -370,9 +370,6 @@
     <t>electricity</t>
   </si>
   <si>
-    <t># Final energy delivery sectors - supplysector characteristics</t>
-  </si>
-  <si>
     <t>rooftop_pv</t>
   </si>
   <si>
@@ -484,9 +481,6 @@
     <t># Electric sector subsector logit exponents</t>
   </si>
   <si>
-    <t>rooftop_PV</t>
-  </si>
-  <si>
     <t>distributed_solar</t>
   </si>
   <si>
@@ -548,9 +542,6 @@
   </si>
   <si>
     <t># Final energy transformation default technology shareweights</t>
-  </si>
-  <si>
-    <t># Final energy delivery input-output coefficients</t>
   </si>
   <si>
     <t># Final energy delivery cost adders</t>
@@ -645,6 +636,24 @@
   <si>
     <t>PalmFruit</t>
   </si>
+  <si>
+    <t>backup-cap-cost</t>
+  </si>
+  <si>
+    <t># Final energy delivery subsector shareweight interpolation</t>
+  </si>
+  <si>
+    <t># Final energy delivery subsector logit exponents</t>
+  </si>
+  <si>
+    <t># Final energy delivery and reliability (backup) sectors - supplysector characteristics</t>
+  </si>
+  <si>
+    <t>CSP gas hybrid mode</t>
+  </si>
+  <si>
+    <t># Final energy delivery input-output efficiencies (global technologies)</t>
+  </si>
 </sst>
 </file>
 
@@ -695,8 +704,72 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1607">
+  <cellStyleXfs count="1671">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2311,7 +2384,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1607">
+  <cellStyles count="1671">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3115,6 +3188,38 @@
     <cellStyle name="Followed Hyperlink" xfId="1602" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1604" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1606" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1608" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1610" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1612" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1614" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1616" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1618" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1620" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1622" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1624" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1626" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1628" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1630" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1632" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1634" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1636" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1638" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1640" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1642" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1644" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1646" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1648" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1650" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1652" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1654" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1656" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1658" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1660" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1662" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1664" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1666" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1668" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1670" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -3918,6 +4023,38 @@
     <cellStyle name="Hyperlink" xfId="1601" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1603" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1605" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1607" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1609" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1611" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1613" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1615" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1617" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1619" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1621" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1623" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1625" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1627" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1629" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1631" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1633" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1635" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1637" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1639" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1641" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1643" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1645" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1647" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1649" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1651" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1653" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1655" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1657" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1659" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1661" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1663" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1665" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1667" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1669" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7909,7 +8046,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7929,10 +8066,10 @@
         <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8009,7 +8146,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8039,7 +8176,7 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>-10</v>
@@ -8050,7 +8187,7 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5">
         <v>-10</v>
@@ -8072,7 +8209,7 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7">
         <v>-6</v>
@@ -8083,7 +8220,7 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8">
         <v>-6</v>
@@ -8094,7 +8231,7 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>-6</v>
@@ -8105,7 +8242,7 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10">
         <v>-6</v>
@@ -8116,7 +8253,7 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11">
         <v>-6</v>
@@ -8127,7 +8264,7 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <v>-6</v>
@@ -8199,7 +8336,7 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
@@ -8213,7 +8350,7 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
@@ -8241,7 +8378,7 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -8255,7 +8392,7 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -8269,7 +8406,7 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>2065</v>
@@ -8283,7 +8420,7 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10">
         <v>2065</v>
@@ -8297,7 +8434,7 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11">
         <v>2065</v>
@@ -8311,7 +8448,7 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -8325,7 +8462,7 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13">
         <v>2020</v>
@@ -8413,7 +8550,7 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
@@ -8433,7 +8570,7 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
@@ -8493,7 +8630,7 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
@@ -8513,7 +8650,7 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
         <v>52</v>
@@ -8533,7 +8670,7 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
         <v>52</v>
@@ -8553,7 +8690,7 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -8573,7 +8710,7 @@
         <v>98</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
         <v>52</v>
@@ -8593,7 +8730,7 @@
         <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
         <v>52</v>
@@ -8613,7 +8750,7 @@
         <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
@@ -8633,7 +8770,7 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
         <v>52</v>
@@ -8653,7 +8790,7 @@
         <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>
@@ -8689,10 +8826,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8713,7 +8850,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4">
         <v>0.25</v>
@@ -8721,7 +8858,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5">
         <v>0.25</v>
@@ -8739,7 +8876,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -8752,12 +8889,12 @@
     <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -8768,36 +8905,42 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" t="s">
         <v>147</v>
       </c>
-      <c r="F2" t="s">
-        <v>149</v>
-      </c>
       <c r="G2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" t="s">
         <v>150</v>
       </c>
-      <c r="H2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
         <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>30</v>
@@ -8808,22 +8951,28 @@
       <c r="H3">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
         <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -8834,22 +8983,28 @@
       <c r="H4">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -8860,22 +9015,28 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
         <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F6">
         <v>30</v>
@@ -8885,6 +9046,12 @@
       </c>
       <c r="H6">
         <v>0.25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -8913,7 +9080,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8959,7 +9126,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -8994,7 +9161,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -9029,7 +9196,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -9061,10 +9228,10 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -9096,10 +9263,10 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9131,10 +9298,10 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -9166,10 +9333,10 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -9201,10 +9368,10 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -9236,10 +9403,10 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -9274,7 +9441,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -9309,7 +9476,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -9344,7 +9511,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -9376,10 +9543,10 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -9411,10 +9578,10 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -9446,10 +9613,10 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -9481,10 +9648,10 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -9516,10 +9683,10 @@
         <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -9551,10 +9718,10 @@
         <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -9586,10 +9753,10 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -9621,10 +9788,10 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -9656,10 +9823,10 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -9691,10 +9858,10 @@
         <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -9726,10 +9893,10 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -9781,7 +9948,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -9839,7 +10006,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -9886,7 +10053,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -9933,7 +10100,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -9977,10 +10144,10 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -10024,10 +10191,10 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -10071,10 +10238,10 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -10118,10 +10285,10 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
         <v>87</v>
@@ -10165,10 +10332,10 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -10212,10 +10379,10 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
         <v>87</v>
@@ -10262,7 +10429,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -10309,7 +10476,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -10356,7 +10523,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -10400,10 +10567,10 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -10447,10 +10614,10 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -10494,13 +10661,13 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -10541,13 +10708,13 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18">
         <v>0.96</v>
@@ -10588,13 +10755,13 @@
         <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -10635,13 +10802,13 @@
         <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -10682,13 +10849,13 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21">
         <v>0.96</v>
@@ -10729,13 +10896,13 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -10776,13 +10943,13 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -10823,13 +10990,13 @@
         <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -10870,13 +11037,13 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25">
         <v>0.1</v>
@@ -10917,13 +11084,13 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -10964,13 +11131,13 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -11034,7 +11201,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -11048,13 +11215,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G2">
         <v>1971</v>
@@ -11095,10 +11262,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E3">
         <v>0.15</v>
@@ -11145,10 +11312,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E4">
         <v>0.15</v>
@@ -11195,10 +11362,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E5">
         <v>0.15</v>
@@ -11242,13 +11409,13 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E6">
         <v>0.15</v>
@@ -11292,13 +11459,13 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E7">
         <v>0.15</v>
@@ -11342,13 +11509,13 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E8">
         <v>0.15</v>
@@ -11392,13 +11559,13 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -11442,13 +11609,13 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -11492,13 +11659,13 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -11545,10 +11712,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E12">
         <v>0.15</v>
@@ -11595,10 +11762,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>0.15</v>
@@ -11645,10 +11812,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -11692,13 +11859,13 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -11742,13 +11909,13 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16">
         <v>0.15</v>
@@ -11792,13 +11959,13 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0.125</v>
@@ -11842,13 +12009,13 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E18">
         <v>0.125</v>
@@ -11892,13 +12059,13 @@
         <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E19">
         <v>0.125</v>
@@ -11942,13 +12109,13 @@
         <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E20">
         <v>0.125</v>
@@ -11992,13 +12159,13 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E21">
         <v>0.125</v>
@@ -12042,13 +12209,13 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E22">
         <v>0.125</v>
@@ -12092,13 +12259,13 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0.125</v>
@@ -12142,13 +12309,13 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0.1</v>
@@ -12213,7 +12380,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -12227,10 +12394,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>1971</v>
@@ -12271,10 +12438,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E3">
         <v>0.8</v>
@@ -12319,10 +12486,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <v>0.8</v>
@@ -12367,10 +12534,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E5">
         <v>0.8</v>
@@ -12412,13 +12579,13 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E6">
         <v>0.8</v>
@@ -12460,13 +12627,13 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7">
         <v>0.8</v>
@@ -12508,13 +12675,13 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E8">
         <v>0.8</v>
@@ -12556,13 +12723,13 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E9">
         <v>0.8</v>
@@ -12604,13 +12771,13 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -12652,13 +12819,13 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E11">
         <v>0.8</v>
@@ -12703,10 +12870,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E12">
         <v>0.8</v>
@@ -12751,10 +12918,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>0.8</v>
@@ -12799,10 +12966,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>0.8</v>
@@ -12844,13 +13011,13 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>0.9</v>
@@ -12891,13 +13058,13 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>0.9</v>
@@ -12939,13 +13106,13 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E17">
         <v>0.45</v>
@@ -12987,13 +13154,13 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>0.45</v>
@@ -13035,13 +13202,13 @@
         <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0.25</v>
@@ -13083,13 +13250,13 @@
         <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -13131,13 +13298,13 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>0.31</v>
@@ -13179,13 +13346,13 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E22">
         <v>0.73</v>
@@ -13227,13 +13394,13 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E23">
         <v>0.9</v>
@@ -13274,13 +13441,13 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E24">
         <v>0.25</v>
@@ -13559,7 +13726,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -13573,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>1971</v>
@@ -13614,10 +13781,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E3" s="3">
         <v>1.472</v>
@@ -13659,10 +13826,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E4" s="3">
         <v>0.93700000000000006</v>
@@ -13704,10 +13871,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E5" s="3">
         <v>1.718</v>
@@ -13746,13 +13913,13 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3">
         <v>1.08</v>
@@ -13791,13 +13958,13 @@
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E7" s="3">
         <v>0.65200000000000002</v>
@@ -13836,13 +14003,13 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E8" s="3">
         <v>0.82699999999999996</v>
@@ -13881,13 +14048,13 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E9" s="3">
         <v>1.08</v>
@@ -13926,13 +14093,13 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" s="3">
         <v>0.84299999999999997</v>
@@ -13971,13 +14138,13 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E11" s="3">
         <v>1.212</v>
@@ -14019,10 +14186,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" s="3">
         <v>1.4930000000000001</v>
@@ -14064,10 +14231,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E13" s="3">
         <v>0.95</v>
@@ -14109,10 +14276,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E14" s="3">
         <v>1.6160000000000001</v>
@@ -14151,13 +14318,13 @@
         <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E15" s="3">
         <v>4.5999999999999999E-2</v>
@@ -14196,13 +14363,13 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E16" s="3">
         <v>0.159</v>
@@ -14241,13 +14408,13 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="3">
         <v>2.2799999999999998</v>
@@ -14286,13 +14453,13 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" s="3">
         <v>3.9089999999999998</v>
@@ -14356,7 +14523,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -14396,7 +14563,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
         <v>49</v>
@@ -14419,10 +14586,10 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
@@ -14445,10 +14612,10 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
         <v>49</v>
@@ -14471,10 +14638,10 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>49</v>
@@ -14500,7 +14667,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>49</v>
@@ -14523,10 +14690,10 @@
         <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
@@ -14549,10 +14716,10 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>49</v>
@@ -14569,10 +14736,10 @@
         <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
         <v>49</v>
@@ -14589,10 +14756,10 @@
         <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
         <v>49</v>
@@ -14609,10 +14776,10 @@
         <v>98</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -14632,7 +14799,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -14652,7 +14819,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
         <v>53</v>
@@ -14672,7 +14839,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>53</v>
@@ -14689,10 +14856,10 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>53</v>
@@ -14709,10 +14876,10 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>53</v>
@@ -14729,10 +14896,10 @@
         <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>53</v>
@@ -14749,10 +14916,10 @@
         <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
         <v>53</v>
@@ -14769,10 +14936,10 @@
         <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
         <v>53</v>
@@ -14789,10 +14956,10 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
         <v>53</v>
@@ -14812,7 +14979,7 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
         <v>53</v>
@@ -14832,7 +14999,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
         <v>53</v>
@@ -14852,7 +15019,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
         <v>53</v>
@@ -14869,10 +15036,10 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
         <v>53</v>
@@ -14889,10 +15056,10 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>53</v>
@@ -14909,10 +15076,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>53</v>
@@ -14929,10 +15096,10 @@
         <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>53</v>
@@ -14949,10 +15116,10 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>53</v>
@@ -14969,10 +15136,10 @@
         <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>53</v>
@@ -14989,10 +15156,10 @@
         <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>53</v>
@@ -15009,10 +15176,10 @@
         <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>53</v>
@@ -15048,7 +15215,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -15088,7 +15255,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <v>0.91</v>
@@ -15114,10 +15281,10 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4">
         <v>0.91</v>
@@ -15143,10 +15310,10 @@
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5">
         <v>0.91</v>
@@ -15175,7 +15342,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6">
         <v>0.91</v>
@@ -15221,7 +15388,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15243,7 +15410,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -15286,7 +15453,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -15302,7 +15469,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -15313,7 +15480,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -15324,10 +15491,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5">
         <v>-6</v>
@@ -15335,10 +15502,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6">
         <v>-6</v>
@@ -15372,7 +15539,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15394,7 +15561,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -15408,7 +15575,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -15422,10 +15589,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
@@ -15436,10 +15603,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
@@ -15476,7 +15643,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -15504,7 +15671,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -15524,7 +15691,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -15544,10 +15711,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
@@ -15564,10 +15731,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
         <v>52</v>
@@ -15606,7 +15773,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15652,7 +15819,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -15693,7 +15860,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -15734,13 +15901,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -15775,13 +15942,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -15838,7 +16005,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15863,7 +16030,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -15883,7 +16050,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -15903,13 +16070,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -15923,13 +16090,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
@@ -15964,7 +16131,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15986,7 +16153,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -16003,7 +16170,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -16020,13 +16187,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -16037,13 +16204,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -16366,7 +16533,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -16388,7 +16555,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -16405,7 +16572,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -16422,7 +16589,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -16439,7 +16606,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -16482,7 +16649,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16498,7 +16665,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -16509,10 +16676,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>-10</v>
@@ -16520,7 +16687,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -16531,10 +16698,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>-10</v>
@@ -16542,7 +16709,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>98</v>
@@ -16553,10 +16720,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>-10</v>
@@ -16564,10 +16731,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9">
         <v>-10</v>
@@ -16575,10 +16742,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10">
         <v>-6</v>
@@ -16586,7 +16753,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
         <v>98</v>
@@ -16597,10 +16764,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C12">
         <v>-6</v>
@@ -16608,10 +16775,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13">
         <v>-6</v>
@@ -16619,10 +16786,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14">
         <v>-6</v>
@@ -16655,7 +16822,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -16677,7 +16844,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -16691,10 +16858,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
@@ -16705,7 +16872,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -16719,10 +16886,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
@@ -16733,7 +16900,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>98</v>
@@ -16747,10 +16914,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -16761,10 +16928,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -16775,10 +16942,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
@@ -16789,7 +16956,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
         <v>98</v>
@@ -16803,10 +16970,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -16817,10 +16984,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
@@ -16831,10 +16998,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
@@ -16845,7 +17012,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -16859,10 +17026,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16">
         <v>2020</v>
@@ -16873,7 +17040,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -16887,10 +17054,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18">
         <v>2020</v>
@@ -16901,7 +17068,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
         <v>98</v>
@@ -16915,10 +17082,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20">
         <v>2020</v>
@@ -16929,10 +17096,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21">
         <v>2020</v>
@@ -16943,10 +17110,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22">
         <v>2020</v>
@@ -16957,7 +17124,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
         <v>98</v>
@@ -16971,10 +17138,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C24">
         <v>2020</v>
@@ -16985,10 +17152,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C25">
         <v>2020</v>
@@ -16999,10 +17166,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C26">
         <v>2020</v>
@@ -17036,7 +17203,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17079,13 +17246,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -17117,13 +17284,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -17155,13 +17322,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -17194,13 +17361,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -17233,13 +17400,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -17271,13 +17438,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -17309,13 +17476,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -17347,13 +17514,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -17385,13 +17552,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
@@ -17423,13 +17590,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -17461,13 +17628,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -17499,13 +17666,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
@@ -17537,13 +17704,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
@@ -17575,13 +17742,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -17613,13 +17780,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
         <v>57</v>
@@ -17674,7 +17841,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17717,13 +17884,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -17755,13 +17922,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -17793,13 +17960,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
@@ -17831,13 +17998,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
         <v>2</v>
@@ -17869,13 +18036,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -17907,13 +18074,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -17945,13 +18112,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -17983,13 +18150,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
@@ -18021,16 +18188,16 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="1">
         <v>0.626</v>
@@ -18059,16 +18226,16 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" s="1">
         <v>0.626</v>
@@ -18097,13 +18264,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -18135,13 +18302,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
         <v>36</v>
@@ -18173,16 +18340,16 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -18211,16 +18378,16 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -18249,16 +18416,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -18308,7 +18475,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -18330,13 +18497,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -18347,13 +18514,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -18364,13 +18531,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -18381,13 +18548,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -18398,13 +18565,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -18415,13 +18582,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -18432,13 +18599,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -18449,13 +18616,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -18466,13 +18633,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -18483,13 +18650,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -18500,13 +18667,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -18517,13 +18684,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -18534,13 +18701,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -18551,13 +18718,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -18568,13 +18735,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -18607,7 +18774,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -18641,13 +18808,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D3">
         <v>0.91</v>
@@ -18670,13 +18837,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D4">
         <v>0.91</v>
@@ -18699,13 +18866,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D5">
         <v>0.91</v>
@@ -18739,7 +18906,7 @@
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -18751,7 +18918,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -18773,7 +18940,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -18790,7 +18957,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -18807,7 +18974,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -18824,7 +18991,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -18841,7 +19008,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -18858,7 +19025,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -18875,7 +19042,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -18892,7 +19059,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -18909,7 +19076,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -18926,7 +19093,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -18943,7 +19110,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -18955,6 +19122,40 @@
         <v>32</v>
       </c>
       <c r="E13">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15">
         <v>-3</v>
       </c>
     </row>
@@ -18971,7 +19172,7 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -18986,7 +19187,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -19002,10 +19203,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>-6</v>
@@ -19013,10 +19214,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>-6</v>
@@ -19024,10 +19225,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>-6</v>
@@ -19035,10 +19236,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>-6</v>
@@ -19046,10 +19247,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>-6</v>
@@ -19057,10 +19258,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>-6</v>
@@ -19068,10 +19269,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>-6</v>
@@ -19079,10 +19280,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>-6</v>
@@ -19090,10 +19291,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>-6</v>
@@ -19101,10 +19302,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C12">
         <v>-6</v>
@@ -19112,12 +19313,34 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>87</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>-6</v>
       </c>
     </row>
@@ -19134,7 +19357,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -19149,7 +19372,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -19171,10 +19394,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
@@ -19185,10 +19408,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
@@ -19199,10 +19422,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
@@ -19213,10 +19436,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
@@ -19227,10 +19450,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -19241,10 +19464,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -19255,10 +19478,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -19269,10 +19492,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
@@ -19283,10 +19506,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
@@ -19297,10 +19520,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -19311,15 +19534,43 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
       </c>
       <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
@@ -19538,7 +19789,7 @@
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
@@ -19558,7 +19809,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -19578,7 +19829,7 @@
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -19616,7 +19867,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -19875,7 +20126,7 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -19886,7 +20137,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -19917,143 +20168,143 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
       </c>
       <c r="E3">
-        <v>0.14000000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="F3">
-        <v>0.14000000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>0.14000000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="H3">
-        <v>0.14000000000000001</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
       </c>
       <c r="E4">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
       </c>
       <c r="E5">
-        <v>1.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F5">
-        <v>1.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G5">
-        <v>1.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H5">
-        <v>1.25</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
       </c>
       <c r="E6">
-        <v>3.03</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F6">
-        <v>3.03</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G6">
-        <v>2.81</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H6">
-        <v>1.79</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="F7">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G7">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
       <c r="H7">
-        <v>0.44</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -20073,91 +20324,91 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
       </c>
       <c r="E11">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -20177,27 +20428,79 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H13">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
@@ -20214,22 +20517,23 @@
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -20246,118 +20550,136 @@
         <v>1971</v>
       </c>
       <c r="F2">
+        <v>2005</v>
+      </c>
+      <c r="G2">
         <v>2100</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>0.377</v>
+      </c>
+      <c r="F3">
+        <v>0.377</v>
+      </c>
+      <c r="G3">
+        <v>0.42799999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>0.307</v>
+      </c>
+      <c r="F4">
+        <v>0.307</v>
+      </c>
+      <c r="G4">
+        <v>0.35799999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D7" t="s">
         <v>98</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -20368,104 +20690,168 @@
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>86</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>86</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>86</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>80</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>80</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
@@ -20485,7 +20871,7 @@
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
@@ -20495,7 +20881,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -20517,13 +20903,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -20534,13 +20920,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -20551,13 +20937,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -20568,13 +20954,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -20585,13 +20971,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -20602,13 +20988,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -20619,13 +21005,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -20636,13 +21022,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -20653,13 +21039,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -20670,13 +21056,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -20687,18 +21073,52 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>87</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
@@ -20990,7 +21410,7 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E10" s="3">
         <v>111.78730206783794</v>
@@ -21013,7 +21433,7 @@
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E11" s="3">
         <v>582.47719635002909</v>
@@ -21033,10 +21453,10 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -21056,10 +21476,10 @@
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E13" s="3">
         <v>142.57460317460317</v>
@@ -21079,10 +21499,10 @@
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E14" s="3">
         <v>128</v>
@@ -21347,7 +21767,7 @@
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -21364,7 +21784,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -21381,7 +21801,7 @@
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D13">
         <v>0</v>

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="4580" yWindow="0" windowWidth="25840" windowHeight="22540" tabRatio="684" firstSheet="47" activeTab="51"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15960" tabRatio="684" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -704,8 +704,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1671">
+  <cellStyleXfs count="1675">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2384,7 +2388,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1671">
+  <cellStyles count="1675">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3220,6 +3224,8 @@
     <cellStyle name="Followed Hyperlink" xfId="1666" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1668" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1670" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1672" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1674" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -4055,6 +4061,8 @@
     <cellStyle name="Hyperlink" xfId="1665" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1667" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1669" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1671" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1673" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -21736,10 +21744,10 @@
         <v>82</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -21753,10 +21761,10 @@
         <v>84</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15960" tabRatio="684" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="32140" windowHeight="21340" tabRatio="684" firstSheet="43" activeTab="43"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -16,50 +16,53 @@
     <sheet name="A21.globaltech_coef.csv" sheetId="22" r:id="rId7"/>
     <sheet name="A21.tradedtech_coef.csv" sheetId="13" r:id="rId8"/>
     <sheet name="A21.globaltech_shrwt.csv" sheetId="23" r:id="rId9"/>
-    <sheet name="A21.tradedtech_shrwt.csv" sheetId="24" r:id="rId10"/>
-    <sheet name="A22.sector.csv" sheetId="9" r:id="rId11"/>
-    <sheet name="A22.subsector_logit.csv" sheetId="25" r:id="rId12"/>
-    <sheet name="A22.subsector_shrwt.csv" sheetId="8" r:id="rId13"/>
-    <sheet name="A22.subsector_interp.csv" sheetId="26" r:id="rId14"/>
-    <sheet name="A22.globaltech_cost.csv" sheetId="27" r:id="rId15"/>
-    <sheet name="A22.globaltech_coef.csv" sheetId="3" r:id="rId16"/>
-    <sheet name="A22.globaltech_shrwt.csv" sheetId="29" r:id="rId17"/>
-    <sheet name="A22.globaltech_retirement.csv" sheetId="28" r:id="rId18"/>
-    <sheet name="A22.globaltech_co2capture.csv" sheetId="30" r:id="rId19"/>
-    <sheet name="A23.sector.csv" sheetId="35" r:id="rId20"/>
-    <sheet name="A23.subsector_logit.csv" sheetId="37" r:id="rId21"/>
-    <sheet name="A23.subsector_shrwt.csv" sheetId="38" r:id="rId22"/>
-    <sheet name="A23.subsector_interp.csv" sheetId="39" r:id="rId23"/>
-    <sheet name="A23.chp_elecratio.csv" sheetId="42" r:id="rId24"/>
-    <sheet name="A23.globalinttech.csv" sheetId="49" r:id="rId25"/>
-    <sheet name="A23.globaltech_shrwt.csv" sheetId="45" r:id="rId26"/>
-    <sheet name="A23.globaltech_eff.csv" sheetId="43" r:id="rId27"/>
-    <sheet name="A23.globaltech_capital.csv" sheetId="46" r:id="rId28"/>
-    <sheet name="A23.globaltech_OMfixed.csv" sheetId="47" r:id="rId29"/>
-    <sheet name="A23.globaltech_OMvar.csv" sheetId="44" r:id="rId30"/>
-    <sheet name="A23.globaltech_retirement.csv" sheetId="48" r:id="rId31"/>
-    <sheet name="A23.globaltech_co2capture.csv" sheetId="50" r:id="rId32"/>
-    <sheet name="A24.sector.csv" sheetId="53" r:id="rId33"/>
-    <sheet name="A24.subsector_logit.csv" sheetId="54" r:id="rId34"/>
-    <sheet name="A24.subsector_shrwt.csv" sheetId="55" r:id="rId35"/>
-    <sheet name="A24.subsector_interp.csv" sheetId="56" r:id="rId36"/>
-    <sheet name="A24.globaltech_cost.csv" sheetId="57" r:id="rId37"/>
-    <sheet name="A24.globaltech_coef.csv" sheetId="58" r:id="rId38"/>
-    <sheet name="A24.globaltech_shrwt.csv" sheetId="59" r:id="rId39"/>
-    <sheet name="A25.sector.csv" sheetId="60" r:id="rId40"/>
-    <sheet name="A25.subsector_logit.csv" sheetId="61" r:id="rId41"/>
-    <sheet name="A25.subsector_shrwt.csv" sheetId="62" r:id="rId42"/>
-    <sheet name="A25.globaltech_cost.csv" sheetId="64" r:id="rId43"/>
-    <sheet name="A25.globaltech_eff.csv" sheetId="65" r:id="rId44"/>
-    <sheet name="A25.globaltech_shrwt.csv" sheetId="66" r:id="rId45"/>
-    <sheet name="A25.globaltech_co2capture.csv" sheetId="67" r:id="rId46"/>
-    <sheet name="A26.sector.csv" sheetId="6" r:id="rId47"/>
-    <sheet name="A26.subsector_logit.csv" sheetId="32" r:id="rId48"/>
-    <sheet name="A26.subsector_shrwt.csv" sheetId="33" r:id="rId49"/>
-    <sheet name="A26.subsector_interp.csv" sheetId="51" r:id="rId50"/>
-    <sheet name="A26.globaltech_cost.csv" sheetId="31" r:id="rId51"/>
-    <sheet name="A26.globaltech_eff.csv" sheetId="7" r:id="rId52"/>
-    <sheet name="A26.globaltech_shrwt.csv" sheetId="52" r:id="rId53"/>
+    <sheet name="A21.globaltech_keyword.csv" sheetId="68" r:id="rId10"/>
+    <sheet name="A21.tradedtech_shrwt.csv" sheetId="24" r:id="rId11"/>
+    <sheet name="A22.sector.csv" sheetId="9" r:id="rId12"/>
+    <sheet name="A22.subsector_logit.csv" sheetId="25" r:id="rId13"/>
+    <sheet name="A22.subsector_shrwt.csv" sheetId="8" r:id="rId14"/>
+    <sheet name="A22.subsector_interp.csv" sheetId="26" r:id="rId15"/>
+    <sheet name="A22.globaltech_cost.csv" sheetId="27" r:id="rId16"/>
+    <sheet name="A22.globaltech_coef.csv" sheetId="3" r:id="rId17"/>
+    <sheet name="A22.globaltech_shrwt.csv" sheetId="29" r:id="rId18"/>
+    <sheet name="A22.globaltech_retirement.csv" sheetId="28" r:id="rId19"/>
+    <sheet name="A22.globaltech_co2capture.csv" sheetId="30" r:id="rId20"/>
+    <sheet name="A23.sector.csv" sheetId="35" r:id="rId21"/>
+    <sheet name="A23.subsector_logit.csv" sheetId="37" r:id="rId22"/>
+    <sheet name="A23.subsector_shrwt.csv" sheetId="38" r:id="rId23"/>
+    <sheet name="A23.subsector_interp.csv" sheetId="39" r:id="rId24"/>
+    <sheet name="A23.chp_elecratio.csv" sheetId="42" r:id="rId25"/>
+    <sheet name="A23.globalinttech.csv" sheetId="49" r:id="rId26"/>
+    <sheet name="A23.globaltech_shrwt.csv" sheetId="45" r:id="rId27"/>
+    <sheet name="A23.globaltech_keyword.csv" sheetId="69" r:id="rId28"/>
+    <sheet name="A23.globaltech_eff.csv" sheetId="43" r:id="rId29"/>
+    <sheet name="A23.globaltech_capital.csv" sheetId="46" r:id="rId30"/>
+    <sheet name="A23.globaltech_OMfixed.csv" sheetId="47" r:id="rId31"/>
+    <sheet name="A23.globaltech_OMvar.csv" sheetId="44" r:id="rId32"/>
+    <sheet name="A23.globaltech_retirement.csv" sheetId="48" r:id="rId33"/>
+    <sheet name="A23.globaltech_co2capture.csv" sheetId="50" r:id="rId34"/>
+    <sheet name="A24.sector.csv" sheetId="53" r:id="rId35"/>
+    <sheet name="A24.subsector_logit.csv" sheetId="54" r:id="rId36"/>
+    <sheet name="A24.subsector_shrwt.csv" sheetId="55" r:id="rId37"/>
+    <sheet name="A24.subsector_interp.csv" sheetId="56" r:id="rId38"/>
+    <sheet name="A24.globaltech_cost.csv" sheetId="57" r:id="rId39"/>
+    <sheet name="A24.globaltech_coef.csv" sheetId="58" r:id="rId40"/>
+    <sheet name="A24.globaltech_shrwt.csv" sheetId="59" r:id="rId41"/>
+    <sheet name="A25.sector.csv" sheetId="60" r:id="rId42"/>
+    <sheet name="A25.subsector_logit.csv" sheetId="61" r:id="rId43"/>
+    <sheet name="A25.globaltech_keyword.csv" sheetId="71" r:id="rId44"/>
+    <sheet name="A25.subsector_shrwt.csv" sheetId="62" r:id="rId45"/>
+    <sheet name="A25.globaltech_cost.csv" sheetId="64" r:id="rId46"/>
+    <sheet name="A25.globaltech_eff.csv" sheetId="65" r:id="rId47"/>
+    <sheet name="A25.globaltech_shrwt.csv" sheetId="66" r:id="rId48"/>
+    <sheet name="A25.globaltech_co2capture.csv" sheetId="67" r:id="rId49"/>
+    <sheet name="A26.sector.csv" sheetId="6" r:id="rId50"/>
+    <sheet name="A26.subsector_logit.csv" sheetId="32" r:id="rId51"/>
+    <sheet name="A26.subsector_shrwt.csv" sheetId="33" r:id="rId52"/>
+    <sheet name="A26.subsector_interp.csv" sheetId="51" r:id="rId53"/>
+    <sheet name="A26.globaltech_cost.csv" sheetId="31" r:id="rId54"/>
+    <sheet name="A26.globaltech_eff.csv" sheetId="7" r:id="rId55"/>
+    <sheet name="A26.globaltech_shrwt.csv" sheetId="52" r:id="rId56"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -71,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="208">
   <si>
     <t>technology</t>
   </si>
@@ -654,6 +657,48 @@
   <si>
     <t># Final energy delivery input-output efficiencies (global technologies)</t>
   </si>
+  <si>
+    <t># Primary energy handling keywords</t>
+  </si>
+  <si>
+    <t>primary.consumption</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>primary.renewable</t>
+  </si>
+  <si>
+    <t>average.fossil.efficiency</t>
+  </si>
+  <si>
+    <t>nuclear-elect</t>
+  </si>
+  <si>
+    <t>hydro-elect</t>
+  </si>
+  <si>
+    <t>wind-elect</t>
+  </si>
+  <si>
+    <t>solar-elect</t>
+  </si>
+  <si>
+    <t>geothermal-elect</t>
+  </si>
+  <si>
+    <t>nuclear-H2</t>
+  </si>
+  <si>
+    <t>wind-H2</t>
+  </si>
+  <si>
+    <t>solar-H2</t>
+  </si>
+  <si>
+    <t># Hydrogen technology keywords</t>
+  </si>
 </sst>
 </file>
 
@@ -662,7 +707,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -686,6 +731,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -704,7 +756,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1675">
+  <cellStyleXfs count="1685">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2380,15 +2432,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1675">
+  <cellStyles count="1685">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3226,6 +3289,11 @@
     <cellStyle name="Followed Hyperlink" xfId="1670" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1672" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1674" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1676" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1678" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1680" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1682" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1684" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -4063,6 +4131,11 @@
     <cellStyle name="Hyperlink" xfId="1669" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1671" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1673" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1675" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1677" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1679" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1681" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1683" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4620,20 +4693,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="4" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -4644,33 +4716,77 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1971</v>
-      </c>
-      <c r="F2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="D7" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4686,6 +4802,72 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="4" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1971</v>
+      </c>
+      <c r="F2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -4796,7 +4978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -4937,7 +5119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -5111,7 +5293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -5343,7 +5525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -5833,7 +6015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -6462,7 +6644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -7011,7 +7193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -7701,152 +7883,6 @@
       </c>
       <c r="I30">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1971</v>
-      </c>
-      <c r="E2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="E3">
-        <v>0.81799999999999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="E4">
-        <v>0.98099999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5">
-        <v>0.26</v>
-      </c>
-      <c r="E5">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.99199999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="E7">
-        <v>0.81799999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8">
-        <v>0.98</v>
-      </c>
-      <c r="E8">
-        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -8042,6 +8078,152 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1971</v>
+      </c>
+      <c r="E2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="E3">
+        <v>0.81799999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="E4">
+        <v>0.98099999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5">
+        <v>0.26</v>
+      </c>
+      <c r="E5">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.99199999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="E7">
+        <v>0.81799999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8">
+        <v>0.98</v>
+      </c>
+      <c r="E8">
+        <v>0.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -8137,7 +8319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8289,7 +8471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8490,7 +8672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8824,7 +9006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8882,7 +9064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -9073,7 +9255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -9942,7 +10124,373 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -11179,2316 +11727,6 @@
       </c>
       <c r="O27">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G2">
-        <v>1971</v>
-      </c>
-      <c r="H2">
-        <v>1990</v>
-      </c>
-      <c r="I2">
-        <v>2005</v>
-      </c>
-      <c r="J2">
-        <v>2020</v>
-      </c>
-      <c r="K2">
-        <v>2035</v>
-      </c>
-      <c r="L2">
-        <v>2050</v>
-      </c>
-      <c r="M2">
-        <v>2065</v>
-      </c>
-      <c r="N2">
-        <v>2080</v>
-      </c>
-      <c r="O2">
-        <v>2095</v>
-      </c>
-      <c r="P2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3">
-        <v>0.15</v>
-      </c>
-      <c r="F3">
-        <v>0.8</v>
-      </c>
-      <c r="G3">
-        <v>496</v>
-      </c>
-      <c r="H3">
-        <v>496</v>
-      </c>
-      <c r="I3">
-        <v>496</v>
-      </c>
-      <c r="J3">
-        <v>496</v>
-      </c>
-      <c r="K3">
-        <v>467</v>
-      </c>
-      <c r="L3">
-        <v>440</v>
-      </c>
-      <c r="M3">
-        <v>414</v>
-      </c>
-      <c r="N3">
-        <v>390</v>
-      </c>
-      <c r="O3">
-        <v>367</v>
-      </c>
-      <c r="P3">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4">
-        <v>0.15</v>
-      </c>
-      <c r="F4">
-        <v>0.8</v>
-      </c>
-      <c r="G4">
-        <v>575</v>
-      </c>
-      <c r="H4">
-        <v>575</v>
-      </c>
-      <c r="I4">
-        <v>575</v>
-      </c>
-      <c r="J4">
-        <v>575</v>
-      </c>
-      <c r="K4">
-        <v>517</v>
-      </c>
-      <c r="L4">
-        <v>437</v>
-      </c>
-      <c r="M4">
-        <v>433</v>
-      </c>
-      <c r="N4">
-        <v>410</v>
-      </c>
-      <c r="O4">
-        <v>402</v>
-      </c>
-      <c r="P4">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5">
-        <v>0.15</v>
-      </c>
-      <c r="F5">
-        <v>0.8</v>
-      </c>
-      <c r="G5">
-        <v>758</v>
-      </c>
-      <c r="H5">
-        <v>758</v>
-      </c>
-      <c r="I5">
-        <v>758</v>
-      </c>
-      <c r="J5">
-        <v>758</v>
-      </c>
-      <c r="K5">
-        <v>666</v>
-      </c>
-      <c r="L5">
-        <v>558</v>
-      </c>
-      <c r="M5">
-        <v>550</v>
-      </c>
-      <c r="N5">
-        <v>522</v>
-      </c>
-      <c r="O5">
-        <v>512</v>
-      </c>
-      <c r="P5">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6">
-        <v>0.15</v>
-      </c>
-      <c r="F6">
-        <v>0.8</v>
-      </c>
-      <c r="G6">
-        <v>158</v>
-      </c>
-      <c r="H6">
-        <v>158</v>
-      </c>
-      <c r="I6">
-        <v>158</v>
-      </c>
-      <c r="J6">
-        <v>163</v>
-      </c>
-      <c r="K6">
-        <v>154</v>
-      </c>
-      <c r="L6">
-        <v>145</v>
-      </c>
-      <c r="M6">
-        <v>136</v>
-      </c>
-      <c r="N6">
-        <v>128</v>
-      </c>
-      <c r="O6">
-        <v>121</v>
-      </c>
-      <c r="P6">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7">
-        <v>0.15</v>
-      </c>
-      <c r="F7">
-        <v>0.8</v>
-      </c>
-      <c r="G7">
-        <v>233</v>
-      </c>
-      <c r="H7">
-        <v>233</v>
-      </c>
-      <c r="I7">
-        <v>233</v>
-      </c>
-      <c r="J7">
-        <v>233</v>
-      </c>
-      <c r="K7">
-        <v>203</v>
-      </c>
-      <c r="L7">
-        <v>177</v>
-      </c>
-      <c r="M7">
-        <v>173</v>
-      </c>
-      <c r="N7">
-        <v>166</v>
-      </c>
-      <c r="O7">
-        <v>163</v>
-      </c>
-      <c r="P7">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8">
-        <v>0.15</v>
-      </c>
-      <c r="F8">
-        <v>0.8</v>
-      </c>
-      <c r="G8">
-        <v>362</v>
-      </c>
-      <c r="H8">
-        <v>362</v>
-      </c>
-      <c r="I8">
-        <v>362</v>
-      </c>
-      <c r="J8">
-        <v>362</v>
-      </c>
-      <c r="K8">
-        <v>313</v>
-      </c>
-      <c r="L8">
-        <v>273</v>
-      </c>
-      <c r="M8">
-        <v>265</v>
-      </c>
-      <c r="N8">
-        <v>254</v>
-      </c>
-      <c r="O8">
-        <v>250</v>
-      </c>
-      <c r="P8">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9">
-        <v>0.15</v>
-      </c>
-      <c r="F9">
-        <v>0.8</v>
-      </c>
-      <c r="G9">
-        <v>158</v>
-      </c>
-      <c r="H9">
-        <v>158</v>
-      </c>
-      <c r="I9">
-        <v>158</v>
-      </c>
-      <c r="J9">
-        <v>163</v>
-      </c>
-      <c r="K9">
-        <v>154</v>
-      </c>
-      <c r="L9">
-        <v>145</v>
-      </c>
-      <c r="M9">
-        <v>136</v>
-      </c>
-      <c r="N9">
-        <v>128</v>
-      </c>
-      <c r="O9">
-        <v>121</v>
-      </c>
-      <c r="P9">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10">
-        <v>0.15</v>
-      </c>
-      <c r="F10">
-        <v>0.8</v>
-      </c>
-      <c r="G10">
-        <v>517</v>
-      </c>
-      <c r="H10">
-        <v>517</v>
-      </c>
-      <c r="I10">
-        <v>517</v>
-      </c>
-      <c r="J10">
-        <v>517</v>
-      </c>
-      <c r="K10">
-        <v>451</v>
-      </c>
-      <c r="L10">
-        <v>393</v>
-      </c>
-      <c r="M10">
-        <v>384</v>
-      </c>
-      <c r="N10">
-        <v>368</v>
-      </c>
-      <c r="O10">
-        <v>362</v>
-      </c>
-      <c r="P10">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11">
-        <v>0.15</v>
-      </c>
-      <c r="F11">
-        <v>0.8</v>
-      </c>
-      <c r="G11">
-        <v>741</v>
-      </c>
-      <c r="H11">
-        <v>741</v>
-      </c>
-      <c r="I11">
-        <v>741</v>
-      </c>
-      <c r="J11">
-        <v>741</v>
-      </c>
-      <c r="K11">
-        <v>641</v>
-      </c>
-      <c r="L11">
-        <v>558</v>
-      </c>
-      <c r="M11">
-        <v>543</v>
-      </c>
-      <c r="N11">
-        <v>521</v>
-      </c>
-      <c r="O11">
-        <v>513</v>
-      </c>
-      <c r="P11">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12">
-        <v>0.15</v>
-      </c>
-      <c r="F12">
-        <v>0.8</v>
-      </c>
-      <c r="G12">
-        <v>511</v>
-      </c>
-      <c r="H12">
-        <v>511</v>
-      </c>
-      <c r="I12">
-        <v>511</v>
-      </c>
-      <c r="J12">
-        <v>511</v>
-      </c>
-      <c r="K12">
-        <v>481</v>
-      </c>
-      <c r="L12">
-        <v>453</v>
-      </c>
-      <c r="M12">
-        <v>427</v>
-      </c>
-      <c r="N12">
-        <v>402</v>
-      </c>
-      <c r="O12">
-        <v>378</v>
-      </c>
-      <c r="P12">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13">
-        <v>0.15</v>
-      </c>
-      <c r="F13">
-        <v>0.8</v>
-      </c>
-      <c r="G13">
-        <v>592</v>
-      </c>
-      <c r="H13">
-        <v>592</v>
-      </c>
-      <c r="I13">
-        <v>592</v>
-      </c>
-      <c r="J13">
-        <v>592</v>
-      </c>
-      <c r="K13">
-        <v>533</v>
-      </c>
-      <c r="L13">
-        <v>450</v>
-      </c>
-      <c r="M13">
-        <v>446</v>
-      </c>
-      <c r="N13">
-        <v>423</v>
-      </c>
-      <c r="O13">
-        <v>415</v>
-      </c>
-      <c r="P13">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14">
-        <v>0.15</v>
-      </c>
-      <c r="F14">
-        <v>0.8</v>
-      </c>
-      <c r="G14">
-        <v>763</v>
-      </c>
-      <c r="H14">
-        <v>763</v>
-      </c>
-      <c r="I14">
-        <v>763</v>
-      </c>
-      <c r="J14">
-        <v>763</v>
-      </c>
-      <c r="K14">
-        <v>673</v>
-      </c>
-      <c r="L14">
-        <v>565</v>
-      </c>
-      <c r="M14">
-        <v>558</v>
-      </c>
-      <c r="N14">
-        <v>529</v>
-      </c>
-      <c r="O14">
-        <v>520</v>
-      </c>
-      <c r="P14">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15">
-        <v>0.15</v>
-      </c>
-      <c r="F15">
-        <v>0.9</v>
-      </c>
-      <c r="G15">
-        <v>620</v>
-      </c>
-      <c r="H15">
-        <v>620</v>
-      </c>
-      <c r="I15">
-        <v>620</v>
-      </c>
-      <c r="J15">
-        <v>620</v>
-      </c>
-      <c r="K15">
-        <v>620</v>
-      </c>
-      <c r="L15">
-        <v>620</v>
-      </c>
-      <c r="M15">
-        <v>620</v>
-      </c>
-      <c r="N15">
-        <v>620</v>
-      </c>
-      <c r="O15">
-        <v>620</v>
-      </c>
-      <c r="P15">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16">
-        <v>0.15</v>
-      </c>
-      <c r="F16">
-        <v>0.9</v>
-      </c>
-      <c r="G16">
-        <v>815</v>
-      </c>
-      <c r="H16">
-        <v>815</v>
-      </c>
-      <c r="I16">
-        <v>815</v>
-      </c>
-      <c r="J16">
-        <v>676</v>
-      </c>
-      <c r="K16">
-        <v>664</v>
-      </c>
-      <c r="L16">
-        <v>654</v>
-      </c>
-      <c r="M16">
-        <v>645</v>
-      </c>
-      <c r="N16">
-        <v>636</v>
-      </c>
-      <c r="O16">
-        <v>626</v>
-      </c>
-      <c r="P16">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17">
-        <v>0.125</v>
-      </c>
-      <c r="F17">
-        <v>0.45</v>
-      </c>
-      <c r="G17">
-        <v>380</v>
-      </c>
-      <c r="H17">
-        <v>380</v>
-      </c>
-      <c r="I17">
-        <v>380</v>
-      </c>
-      <c r="J17">
-        <v>366</v>
-      </c>
-      <c r="K17">
-        <v>353</v>
-      </c>
-      <c r="L17">
-        <v>340</v>
-      </c>
-      <c r="M17">
-        <v>327</v>
-      </c>
-      <c r="N17">
-        <v>315</v>
-      </c>
-      <c r="O17">
-        <v>303</v>
-      </c>
-      <c r="P17">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18">
-        <v>0.125</v>
-      </c>
-      <c r="F18">
-        <v>0.45</v>
-      </c>
-      <c r="G18">
-        <v>916</v>
-      </c>
-      <c r="H18">
-        <v>916</v>
-      </c>
-      <c r="I18">
-        <v>916</v>
-      </c>
-      <c r="J18">
-        <v>827</v>
-      </c>
-      <c r="K18">
-        <v>764</v>
-      </c>
-      <c r="L18">
-        <v>721</v>
-      </c>
-      <c r="M18">
-        <v>695</v>
-      </c>
-      <c r="N18">
-        <v>669</v>
-      </c>
-      <c r="O18">
-        <v>645</v>
-      </c>
-      <c r="P18">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19">
-        <v>0.125</v>
-      </c>
-      <c r="F19">
-        <v>0.25</v>
-      </c>
-      <c r="G19">
-        <v>3016</v>
-      </c>
-      <c r="H19">
-        <v>3016</v>
-      </c>
-      <c r="I19">
-        <v>3016</v>
-      </c>
-      <c r="J19">
-        <v>1909</v>
-      </c>
-      <c r="K19">
-        <v>1305</v>
-      </c>
-      <c r="L19">
-        <v>963</v>
-      </c>
-      <c r="M19">
-        <v>767</v>
-      </c>
-      <c r="N19">
-        <v>659</v>
-      </c>
-      <c r="O19">
-        <v>610</v>
-      </c>
-      <c r="P19">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20">
-        <v>0.125</v>
-      </c>
-      <c r="F20">
-        <v>0.25</v>
-      </c>
-      <c r="G20">
-        <v>3552</v>
-      </c>
-      <c r="H20">
-        <v>3552</v>
-      </c>
-      <c r="I20">
-        <v>3552</v>
-      </c>
-      <c r="J20">
-        <v>2370</v>
-      </c>
-      <c r="K20">
-        <v>1716</v>
-      </c>
-      <c r="L20">
-        <v>1345</v>
-      </c>
-      <c r="M20">
-        <v>1135</v>
-      </c>
-      <c r="N20">
-        <v>1013</v>
-      </c>
-      <c r="O20">
-        <v>951</v>
-      </c>
-      <c r="P20">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21">
-        <v>0.125</v>
-      </c>
-      <c r="F21">
-        <v>0.31</v>
-      </c>
-      <c r="G21">
-        <v>1073</v>
-      </c>
-      <c r="H21">
-        <v>1073</v>
-      </c>
-      <c r="I21">
-        <v>1073</v>
-      </c>
-      <c r="J21">
-        <v>995</v>
-      </c>
-      <c r="K21">
-        <v>923</v>
-      </c>
-      <c r="L21">
-        <v>856</v>
-      </c>
-      <c r="M21">
-        <v>794</v>
-      </c>
-      <c r="N21">
-        <v>737</v>
-      </c>
-      <c r="O21">
-        <v>683</v>
-      </c>
-      <c r="P21">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22">
-        <v>0.125</v>
-      </c>
-      <c r="F22">
-        <v>0.73</v>
-      </c>
-      <c r="G22">
-        <v>2146</v>
-      </c>
-      <c r="H22">
-        <v>2146</v>
-      </c>
-      <c r="I22">
-        <v>2146</v>
-      </c>
-      <c r="J22">
-        <v>1991</v>
-      </c>
-      <c r="K22">
-        <v>1846</v>
-      </c>
-      <c r="L22">
-        <v>1713</v>
-      </c>
-      <c r="M22">
-        <v>1589</v>
-      </c>
-      <c r="N22">
-        <v>1474</v>
-      </c>
-      <c r="O22">
-        <v>1367</v>
-      </c>
-      <c r="P22">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23">
-        <v>0.125</v>
-      </c>
-      <c r="F23">
-        <v>0.9</v>
-      </c>
-      <c r="G23" s="2">
-        <v>521</v>
-      </c>
-      <c r="H23" s="2">
-        <v>521</v>
-      </c>
-      <c r="I23" s="2">
-        <v>521</v>
-      </c>
-      <c r="J23" s="2">
-        <v>485</v>
-      </c>
-      <c r="K23" s="2">
-        <v>448</v>
-      </c>
-      <c r="L23" s="2">
-        <v>421</v>
-      </c>
-      <c r="M23" s="2">
-        <v>406</v>
-      </c>
-      <c r="N23" s="2">
-        <v>391</v>
-      </c>
-      <c r="O23" s="2">
-        <v>376</v>
-      </c>
-      <c r="P23" s="2">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24">
-        <v>0.1</v>
-      </c>
-      <c r="F24">
-        <v>0.25</v>
-      </c>
-      <c r="G24">
-        <v>4403</v>
-      </c>
-      <c r="H24">
-        <v>4403</v>
-      </c>
-      <c r="I24">
-        <v>4403</v>
-      </c>
-      <c r="J24">
-        <v>2798</v>
-      </c>
-      <c r="K24">
-        <v>1946</v>
-      </c>
-      <c r="L24">
-        <v>1477</v>
-      </c>
-      <c r="M24">
-        <v>1192</v>
-      </c>
-      <c r="N24">
-        <v>1091</v>
-      </c>
-      <c r="O24">
-        <v>1024</v>
-      </c>
-      <c r="P24">
-        <v>1024</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="6.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2">
-        <v>1971</v>
-      </c>
-      <c r="G2">
-        <v>1990</v>
-      </c>
-      <c r="H2">
-        <v>2005</v>
-      </c>
-      <c r="I2">
-        <v>2020</v>
-      </c>
-      <c r="J2">
-        <v>2035</v>
-      </c>
-      <c r="K2">
-        <v>2050</v>
-      </c>
-      <c r="L2">
-        <v>2065</v>
-      </c>
-      <c r="M2">
-        <v>2080</v>
-      </c>
-      <c r="N2">
-        <v>2095</v>
-      </c>
-      <c r="O2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3">
-        <v>0.8</v>
-      </c>
-      <c r="F3" s="3">
-        <v>8.83</v>
-      </c>
-      <c r="G3" s="3">
-        <v>8.83</v>
-      </c>
-      <c r="H3" s="3">
-        <v>8.83</v>
-      </c>
-      <c r="I3" s="3">
-        <v>8.83</v>
-      </c>
-      <c r="J3" s="3">
-        <v>8.31</v>
-      </c>
-      <c r="K3" s="3">
-        <v>7.83</v>
-      </c>
-      <c r="L3" s="3">
-        <v>7.37</v>
-      </c>
-      <c r="M3" s="3">
-        <v>6.94</v>
-      </c>
-      <c r="N3" s="3">
-        <v>6.54</v>
-      </c>
-      <c r="O3" s="3">
-        <f>N3</f>
-        <v>6.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>0.8</v>
-      </c>
-      <c r="F4" s="3">
-        <v>12.4</v>
-      </c>
-      <c r="G4" s="3">
-        <v>12.4</v>
-      </c>
-      <c r="H4" s="3">
-        <v>12.4</v>
-      </c>
-      <c r="I4" s="3">
-        <v>12.4</v>
-      </c>
-      <c r="J4" s="3">
-        <v>11.57</v>
-      </c>
-      <c r="K4" s="3">
-        <v>10.42</v>
-      </c>
-      <c r="L4" s="3">
-        <v>10.36</v>
-      </c>
-      <c r="M4" s="3">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="N4" s="3">
-        <v>9.92</v>
-      </c>
-      <c r="O4" s="3">
-        <f t="shared" ref="O4:O22" si="0">N4</f>
-        <v>9.92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5">
-        <v>0.8</v>
-      </c>
-      <c r="F5" s="3">
-        <v>14.22</v>
-      </c>
-      <c r="G5" s="3">
-        <v>14.22</v>
-      </c>
-      <c r="H5" s="3">
-        <v>14.22</v>
-      </c>
-      <c r="I5" s="3">
-        <v>14.22</v>
-      </c>
-      <c r="J5" s="3">
-        <v>13.14</v>
-      </c>
-      <c r="K5" s="3">
-        <v>11.79</v>
-      </c>
-      <c r="L5" s="3">
-        <v>11.69</v>
-      </c>
-      <c r="M5" s="3">
-        <v>11.32</v>
-      </c>
-      <c r="N5" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="O5" s="3">
-        <f t="shared" si="0"/>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6">
-        <v>0.8</v>
-      </c>
-      <c r="F6" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="G6" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="I6" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="J6" s="3">
-        <v>3.53</v>
-      </c>
-      <c r="K6" s="3">
-        <v>3.33</v>
-      </c>
-      <c r="L6" s="3">
-        <v>3.13</v>
-      </c>
-      <c r="M6" s="3">
-        <v>2.95</v>
-      </c>
-      <c r="N6" s="3">
-        <v>2.78</v>
-      </c>
-      <c r="O6" s="3">
-        <f t="shared" si="0"/>
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7">
-        <v>0.8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3.88</v>
-      </c>
-      <c r="G7" s="3">
-        <v>3.88</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3.88</v>
-      </c>
-      <c r="I7" s="3">
-        <v>3.88</v>
-      </c>
-      <c r="J7" s="3">
-        <v>3.54</v>
-      </c>
-      <c r="K7" s="3">
-        <v>3.26</v>
-      </c>
-      <c r="L7" s="3">
-        <v>3.21</v>
-      </c>
-      <c r="M7" s="3">
-        <v>3.13</v>
-      </c>
-      <c r="N7" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="O7" s="3">
-        <f t="shared" si="0"/>
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8">
-        <v>0.8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4.29</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4.29</v>
-      </c>
-      <c r="H8" s="3">
-        <v>4.29</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4.29</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3.56</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3.41</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3.38</v>
-      </c>
-      <c r="O8" s="3">
-        <f t="shared" si="0"/>
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9">
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3.53</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3.33</v>
-      </c>
-      <c r="L9" s="3">
-        <v>3.13</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2.95</v>
-      </c>
-      <c r="N9" s="3">
-        <v>2.78</v>
-      </c>
-      <c r="O9" s="3">
-        <f t="shared" si="0"/>
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E10">
-        <v>0.8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>11.16</v>
-      </c>
-      <c r="G10" s="3">
-        <v>11.16</v>
-      </c>
-      <c r="H10" s="3">
-        <v>11.16</v>
-      </c>
-      <c r="I10" s="3">
-        <v>11.16</v>
-      </c>
-      <c r="J10" s="3">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K10" s="3">
-        <v>9.3699999999999992</v>
-      </c>
-      <c r="L10" s="3">
-        <v>9.24</v>
-      </c>
-      <c r="M10" s="3">
-        <v>9.01</v>
-      </c>
-      <c r="N10" s="3">
-        <v>8.93</v>
-      </c>
-      <c r="O10" s="3">
-        <f t="shared" si="0"/>
-        <v>8.93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11">
-        <v>0.8</v>
-      </c>
-      <c r="F11" s="3">
-        <v>12.02</v>
-      </c>
-      <c r="G11" s="3">
-        <v>12.02</v>
-      </c>
-      <c r="H11" s="3">
-        <v>12.02</v>
-      </c>
-      <c r="I11" s="3">
-        <v>12.02</v>
-      </c>
-      <c r="J11" s="3">
-        <v>10.93</v>
-      </c>
-      <c r="K11" s="3">
-        <v>10.01</v>
-      </c>
-      <c r="L11" s="3">
-        <v>9.86</v>
-      </c>
-      <c r="M11" s="3">
-        <v>9.6</v>
-      </c>
-      <c r="N11" s="3">
-        <v>9.51</v>
-      </c>
-      <c r="O11" s="3">
-        <f t="shared" si="0"/>
-        <v>9.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12">
-        <v>0.8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>9.09</v>
-      </c>
-      <c r="G12" s="3">
-        <v>9.09</v>
-      </c>
-      <c r="H12" s="3">
-        <v>9.09</v>
-      </c>
-      <c r="I12" s="3">
-        <v>9.09</v>
-      </c>
-      <c r="J12" s="3">
-        <v>8.56</v>
-      </c>
-      <c r="K12" s="3">
-        <v>8.06</v>
-      </c>
-      <c r="L12" s="3">
-        <v>7.59</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7.15</v>
-      </c>
-      <c r="N12" s="3">
-        <v>6.73</v>
-      </c>
-      <c r="O12" s="3">
-        <f t="shared" si="0"/>
-        <v>6.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13">
-        <v>0.8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>12.77</v>
-      </c>
-      <c r="G13" s="3">
-        <v>12.77</v>
-      </c>
-      <c r="H13" s="3">
-        <v>12.77</v>
-      </c>
-      <c r="I13" s="3">
-        <v>12.77</v>
-      </c>
-      <c r="J13" s="3">
-        <v>11.91</v>
-      </c>
-      <c r="K13" s="3">
-        <v>10.73</v>
-      </c>
-      <c r="L13" s="3">
-        <v>10.67</v>
-      </c>
-      <c r="M13" s="3">
-        <v>10.33</v>
-      </c>
-      <c r="N13" s="3">
-        <v>10.220000000000001</v>
-      </c>
-      <c r="O13" s="3">
-        <f t="shared" si="0"/>
-        <v>10.220000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14">
-        <v>0.8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>14.33</v>
-      </c>
-      <c r="G14" s="3">
-        <v>14.33</v>
-      </c>
-      <c r="H14" s="3">
-        <v>14.33</v>
-      </c>
-      <c r="I14" s="3">
-        <v>14.33</v>
-      </c>
-      <c r="J14" s="3">
-        <v>13.26</v>
-      </c>
-      <c r="K14" s="3">
-        <v>11.9</v>
-      </c>
-      <c r="L14" s="3">
-        <v>11.81</v>
-      </c>
-      <c r="M14" s="3">
-        <v>11.44</v>
-      </c>
-      <c r="N14" s="3">
-        <v>11.31</v>
-      </c>
-      <c r="O14" s="3">
-        <f t="shared" si="0"/>
-        <v>11.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15">
-        <v>0.9</v>
-      </c>
-      <c r="F15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="G15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="H15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="I15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="J15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="K15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="L15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="M15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="N15" s="3">
-        <v>22.02</v>
-      </c>
-      <c r="O15" s="3">
-        <v>22.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16">
-        <v>0.9</v>
-      </c>
-      <c r="F16" s="3">
-        <v>21.77</v>
-      </c>
-      <c r="G16" s="3">
-        <v>21.77</v>
-      </c>
-      <c r="H16" s="3">
-        <v>21.77</v>
-      </c>
-      <c r="I16" s="3">
-        <v>21.77</v>
-      </c>
-      <c r="J16" s="3">
-        <v>21.41</v>
-      </c>
-      <c r="K16" s="3">
-        <v>21.09</v>
-      </c>
-      <c r="L16" s="3">
-        <v>20.77</v>
-      </c>
-      <c r="M16" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="N16" s="3">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="O16" s="3">
-        <f t="shared" si="0"/>
-        <v>20.190000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17">
-        <v>0.45</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3.61</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3.48</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3.35</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3.22</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="O17" s="3">
-        <f t="shared" si="0"/>
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18">
-        <v>0.45</v>
-      </c>
-      <c r="F18" s="3">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="G18" s="3">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="H18" s="3">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="J18" s="3">
-        <v>8.49</v>
-      </c>
-      <c r="K18" s="3">
-        <v>8.36</v>
-      </c>
-      <c r="L18" s="3">
-        <v>8.23</v>
-      </c>
-      <c r="M18" s="3">
-        <v>8.11</v>
-      </c>
-      <c r="N18" s="3">
-        <v>7.99</v>
-      </c>
-      <c r="O18" s="3">
-        <f t="shared" si="0"/>
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19">
-        <v>0.25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>8.93</v>
-      </c>
-      <c r="G19" s="3">
-        <v>8.93</v>
-      </c>
-      <c r="H19" s="3">
-        <v>8.93</v>
-      </c>
-      <c r="I19" s="3">
-        <v>8.93</v>
-      </c>
-      <c r="J19" s="3">
-        <v>7.14</v>
-      </c>
-      <c r="K19" s="3">
-        <v>6.43</v>
-      </c>
-      <c r="L19" s="3">
-        <v>5.71</v>
-      </c>
-      <c r="M19" s="3">
-        <v>5.36</v>
-      </c>
-      <c r="N19" s="3">
-        <v>5.36</v>
-      </c>
-      <c r="O19" s="3">
-        <f t="shared" si="0"/>
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20">
-        <v>0.25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>17.420000000000002</v>
-      </c>
-      <c r="G20" s="3">
-        <v>17.420000000000002</v>
-      </c>
-      <c r="H20" s="3">
-        <v>17.420000000000002</v>
-      </c>
-      <c r="I20" s="3">
-        <v>16.23</v>
-      </c>
-      <c r="J20" s="3">
-        <v>13.66</v>
-      </c>
-      <c r="K20" s="3">
-        <v>12.48</v>
-      </c>
-      <c r="L20" s="3">
-        <v>11.54</v>
-      </c>
-      <c r="M20" s="3">
-        <v>10.97</v>
-      </c>
-      <c r="N20" s="3">
-        <v>10.76</v>
-      </c>
-      <c r="O20" s="3">
-        <f t="shared" si="0"/>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21">
-        <v>0.31</v>
-      </c>
-      <c r="F21" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="G21" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="H21" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="I21" s="3">
-        <v>15.42</v>
-      </c>
-      <c r="J21" s="3">
-        <v>14.3</v>
-      </c>
-      <c r="K21" s="3">
-        <v>13.26</v>
-      </c>
-      <c r="L21" s="3">
-        <v>12.3</v>
-      </c>
-      <c r="M21" s="3">
-        <v>11.41</v>
-      </c>
-      <c r="N21" s="3">
-        <v>10.59</v>
-      </c>
-      <c r="O21" s="3">
-        <f t="shared" si="0"/>
-        <v>10.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22">
-        <v>0.73</v>
-      </c>
-      <c r="F22" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="G22" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="H22" s="3">
-        <v>16.62</v>
-      </c>
-      <c r="I22" s="3">
-        <v>15.42</v>
-      </c>
-      <c r="J22" s="3">
-        <v>14.3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>13.26</v>
-      </c>
-      <c r="L22" s="3">
-        <v>12.3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>11.41</v>
-      </c>
-      <c r="N22" s="3">
-        <v>10.59</v>
-      </c>
-      <c r="O22" s="3">
-        <f t="shared" si="0"/>
-        <v>10.59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23">
-        <v>0.9</v>
-      </c>
-      <c r="F23" s="3">
-        <v>23.54</v>
-      </c>
-      <c r="G23" s="3">
-        <v>23.54</v>
-      </c>
-      <c r="H23" s="3">
-        <v>23.54</v>
-      </c>
-      <c r="I23" s="3">
-        <v>21.91</v>
-      </c>
-      <c r="J23" s="3">
-        <v>20.239999999999998</v>
-      </c>
-      <c r="K23" s="3">
-        <v>19.02</v>
-      </c>
-      <c r="L23" s="3">
-        <v>18.34</v>
-      </c>
-      <c r="M23" s="3">
-        <v>17.670000000000002</v>
-      </c>
-      <c r="N23" s="3">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="O23" s="3">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24">
-        <v>0.25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>46.77</v>
-      </c>
-      <c r="G24" s="3">
-        <v>46.77</v>
-      </c>
-      <c r="H24" s="3">
-        <v>46.77</v>
-      </c>
-      <c r="I24" s="3">
-        <v>22.49</v>
-      </c>
-      <c r="J24" s="3">
-        <v>17.3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>12.48</v>
-      </c>
-      <c r="L24" s="3">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
-        <v>7.69</v>
-      </c>
-      <c r="N24" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="O24" s="3">
-        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -13722,6 +11960,2316 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2">
+        <v>1971</v>
+      </c>
+      <c r="H2">
+        <v>1990</v>
+      </c>
+      <c r="I2">
+        <v>2005</v>
+      </c>
+      <c r="J2">
+        <v>2020</v>
+      </c>
+      <c r="K2">
+        <v>2035</v>
+      </c>
+      <c r="L2">
+        <v>2050</v>
+      </c>
+      <c r="M2">
+        <v>2065</v>
+      </c>
+      <c r="N2">
+        <v>2080</v>
+      </c>
+      <c r="O2">
+        <v>2095</v>
+      </c>
+      <c r="P2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3">
+        <v>0.15</v>
+      </c>
+      <c r="F3">
+        <v>0.8</v>
+      </c>
+      <c r="G3">
+        <v>496</v>
+      </c>
+      <c r="H3">
+        <v>496</v>
+      </c>
+      <c r="I3">
+        <v>496</v>
+      </c>
+      <c r="J3">
+        <v>496</v>
+      </c>
+      <c r="K3">
+        <v>467</v>
+      </c>
+      <c r="L3">
+        <v>440</v>
+      </c>
+      <c r="M3">
+        <v>414</v>
+      </c>
+      <c r="N3">
+        <v>390</v>
+      </c>
+      <c r="O3">
+        <v>367</v>
+      </c>
+      <c r="P3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4">
+        <v>0.15</v>
+      </c>
+      <c r="F4">
+        <v>0.8</v>
+      </c>
+      <c r="G4">
+        <v>575</v>
+      </c>
+      <c r="H4">
+        <v>575</v>
+      </c>
+      <c r="I4">
+        <v>575</v>
+      </c>
+      <c r="J4">
+        <v>575</v>
+      </c>
+      <c r="K4">
+        <v>517</v>
+      </c>
+      <c r="L4">
+        <v>437</v>
+      </c>
+      <c r="M4">
+        <v>433</v>
+      </c>
+      <c r="N4">
+        <v>410</v>
+      </c>
+      <c r="O4">
+        <v>402</v>
+      </c>
+      <c r="P4">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5">
+        <v>0.15</v>
+      </c>
+      <c r="F5">
+        <v>0.8</v>
+      </c>
+      <c r="G5">
+        <v>758</v>
+      </c>
+      <c r="H5">
+        <v>758</v>
+      </c>
+      <c r="I5">
+        <v>758</v>
+      </c>
+      <c r="J5">
+        <v>758</v>
+      </c>
+      <c r="K5">
+        <v>666</v>
+      </c>
+      <c r="L5">
+        <v>558</v>
+      </c>
+      <c r="M5">
+        <v>550</v>
+      </c>
+      <c r="N5">
+        <v>522</v>
+      </c>
+      <c r="O5">
+        <v>512</v>
+      </c>
+      <c r="P5">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6">
+        <v>0.15</v>
+      </c>
+      <c r="F6">
+        <v>0.8</v>
+      </c>
+      <c r="G6">
+        <v>158</v>
+      </c>
+      <c r="H6">
+        <v>158</v>
+      </c>
+      <c r="I6">
+        <v>158</v>
+      </c>
+      <c r="J6">
+        <v>163</v>
+      </c>
+      <c r="K6">
+        <v>154</v>
+      </c>
+      <c r="L6">
+        <v>145</v>
+      </c>
+      <c r="M6">
+        <v>136</v>
+      </c>
+      <c r="N6">
+        <v>128</v>
+      </c>
+      <c r="O6">
+        <v>121</v>
+      </c>
+      <c r="P6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7">
+        <v>0.15</v>
+      </c>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="G7">
+        <v>233</v>
+      </c>
+      <c r="H7">
+        <v>233</v>
+      </c>
+      <c r="I7">
+        <v>233</v>
+      </c>
+      <c r="J7">
+        <v>233</v>
+      </c>
+      <c r="K7">
+        <v>203</v>
+      </c>
+      <c r="L7">
+        <v>177</v>
+      </c>
+      <c r="M7">
+        <v>173</v>
+      </c>
+      <c r="N7">
+        <v>166</v>
+      </c>
+      <c r="O7">
+        <v>163</v>
+      </c>
+      <c r="P7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8">
+        <v>0.15</v>
+      </c>
+      <c r="F8">
+        <v>0.8</v>
+      </c>
+      <c r="G8">
+        <v>362</v>
+      </c>
+      <c r="H8">
+        <v>362</v>
+      </c>
+      <c r="I8">
+        <v>362</v>
+      </c>
+      <c r="J8">
+        <v>362</v>
+      </c>
+      <c r="K8">
+        <v>313</v>
+      </c>
+      <c r="L8">
+        <v>273</v>
+      </c>
+      <c r="M8">
+        <v>265</v>
+      </c>
+      <c r="N8">
+        <v>254</v>
+      </c>
+      <c r="O8">
+        <v>250</v>
+      </c>
+      <c r="P8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9">
+        <v>0.15</v>
+      </c>
+      <c r="F9">
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <v>158</v>
+      </c>
+      <c r="H9">
+        <v>158</v>
+      </c>
+      <c r="I9">
+        <v>158</v>
+      </c>
+      <c r="J9">
+        <v>163</v>
+      </c>
+      <c r="K9">
+        <v>154</v>
+      </c>
+      <c r="L9">
+        <v>145</v>
+      </c>
+      <c r="M9">
+        <v>136</v>
+      </c>
+      <c r="N9">
+        <v>128</v>
+      </c>
+      <c r="O9">
+        <v>121</v>
+      </c>
+      <c r="P9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10">
+        <v>0.15</v>
+      </c>
+      <c r="F10">
+        <v>0.8</v>
+      </c>
+      <c r="G10">
+        <v>517</v>
+      </c>
+      <c r="H10">
+        <v>517</v>
+      </c>
+      <c r="I10">
+        <v>517</v>
+      </c>
+      <c r="J10">
+        <v>517</v>
+      </c>
+      <c r="K10">
+        <v>451</v>
+      </c>
+      <c r="L10">
+        <v>393</v>
+      </c>
+      <c r="M10">
+        <v>384</v>
+      </c>
+      <c r="N10">
+        <v>368</v>
+      </c>
+      <c r="O10">
+        <v>362</v>
+      </c>
+      <c r="P10">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11">
+        <v>0.15</v>
+      </c>
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11">
+        <v>741</v>
+      </c>
+      <c r="H11">
+        <v>741</v>
+      </c>
+      <c r="I11">
+        <v>741</v>
+      </c>
+      <c r="J11">
+        <v>741</v>
+      </c>
+      <c r="K11">
+        <v>641</v>
+      </c>
+      <c r="L11">
+        <v>558</v>
+      </c>
+      <c r="M11">
+        <v>543</v>
+      </c>
+      <c r="N11">
+        <v>521</v>
+      </c>
+      <c r="O11">
+        <v>513</v>
+      </c>
+      <c r="P11">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12">
+        <v>0.15</v>
+      </c>
+      <c r="F12">
+        <v>0.8</v>
+      </c>
+      <c r="G12">
+        <v>511</v>
+      </c>
+      <c r="H12">
+        <v>511</v>
+      </c>
+      <c r="I12">
+        <v>511</v>
+      </c>
+      <c r="J12">
+        <v>511</v>
+      </c>
+      <c r="K12">
+        <v>481</v>
+      </c>
+      <c r="L12">
+        <v>453</v>
+      </c>
+      <c r="M12">
+        <v>427</v>
+      </c>
+      <c r="N12">
+        <v>402</v>
+      </c>
+      <c r="O12">
+        <v>378</v>
+      </c>
+      <c r="P12">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13">
+        <v>0.15</v>
+      </c>
+      <c r="F13">
+        <v>0.8</v>
+      </c>
+      <c r="G13">
+        <v>592</v>
+      </c>
+      <c r="H13">
+        <v>592</v>
+      </c>
+      <c r="I13">
+        <v>592</v>
+      </c>
+      <c r="J13">
+        <v>592</v>
+      </c>
+      <c r="K13">
+        <v>533</v>
+      </c>
+      <c r="L13">
+        <v>450</v>
+      </c>
+      <c r="M13">
+        <v>446</v>
+      </c>
+      <c r="N13">
+        <v>423</v>
+      </c>
+      <c r="O13">
+        <v>415</v>
+      </c>
+      <c r="P13">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14">
+        <v>0.15</v>
+      </c>
+      <c r="F14">
+        <v>0.8</v>
+      </c>
+      <c r="G14">
+        <v>763</v>
+      </c>
+      <c r="H14">
+        <v>763</v>
+      </c>
+      <c r="I14">
+        <v>763</v>
+      </c>
+      <c r="J14">
+        <v>763</v>
+      </c>
+      <c r="K14">
+        <v>673</v>
+      </c>
+      <c r="L14">
+        <v>565</v>
+      </c>
+      <c r="M14">
+        <v>558</v>
+      </c>
+      <c r="N14">
+        <v>529</v>
+      </c>
+      <c r="O14">
+        <v>520</v>
+      </c>
+      <c r="P14">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15">
+        <v>0.15</v>
+      </c>
+      <c r="F15">
+        <v>0.9</v>
+      </c>
+      <c r="G15">
+        <v>620</v>
+      </c>
+      <c r="H15">
+        <v>620</v>
+      </c>
+      <c r="I15">
+        <v>620</v>
+      </c>
+      <c r="J15">
+        <v>620</v>
+      </c>
+      <c r="K15">
+        <v>620</v>
+      </c>
+      <c r="L15">
+        <v>620</v>
+      </c>
+      <c r="M15">
+        <v>620</v>
+      </c>
+      <c r="N15">
+        <v>620</v>
+      </c>
+      <c r="O15">
+        <v>620</v>
+      </c>
+      <c r="P15">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16">
+        <v>0.15</v>
+      </c>
+      <c r="F16">
+        <v>0.9</v>
+      </c>
+      <c r="G16">
+        <v>815</v>
+      </c>
+      <c r="H16">
+        <v>815</v>
+      </c>
+      <c r="I16">
+        <v>815</v>
+      </c>
+      <c r="J16">
+        <v>676</v>
+      </c>
+      <c r="K16">
+        <v>664</v>
+      </c>
+      <c r="L16">
+        <v>654</v>
+      </c>
+      <c r="M16">
+        <v>645</v>
+      </c>
+      <c r="N16">
+        <v>636</v>
+      </c>
+      <c r="O16">
+        <v>626</v>
+      </c>
+      <c r="P16">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17">
+        <v>0.125</v>
+      </c>
+      <c r="F17">
+        <v>0.45</v>
+      </c>
+      <c r="G17">
+        <v>380</v>
+      </c>
+      <c r="H17">
+        <v>380</v>
+      </c>
+      <c r="I17">
+        <v>380</v>
+      </c>
+      <c r="J17">
+        <v>366</v>
+      </c>
+      <c r="K17">
+        <v>353</v>
+      </c>
+      <c r="L17">
+        <v>340</v>
+      </c>
+      <c r="M17">
+        <v>327</v>
+      </c>
+      <c r="N17">
+        <v>315</v>
+      </c>
+      <c r="O17">
+        <v>303</v>
+      </c>
+      <c r="P17">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18">
+        <v>0.125</v>
+      </c>
+      <c r="F18">
+        <v>0.45</v>
+      </c>
+      <c r="G18">
+        <v>916</v>
+      </c>
+      <c r="H18">
+        <v>916</v>
+      </c>
+      <c r="I18">
+        <v>916</v>
+      </c>
+      <c r="J18">
+        <v>827</v>
+      </c>
+      <c r="K18">
+        <v>764</v>
+      </c>
+      <c r="L18">
+        <v>721</v>
+      </c>
+      <c r="M18">
+        <v>695</v>
+      </c>
+      <c r="N18">
+        <v>669</v>
+      </c>
+      <c r="O18">
+        <v>645</v>
+      </c>
+      <c r="P18">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19">
+        <v>0.125</v>
+      </c>
+      <c r="F19">
+        <v>0.25</v>
+      </c>
+      <c r="G19">
+        <v>3016</v>
+      </c>
+      <c r="H19">
+        <v>3016</v>
+      </c>
+      <c r="I19">
+        <v>3016</v>
+      </c>
+      <c r="J19">
+        <v>1909</v>
+      </c>
+      <c r="K19">
+        <v>1305</v>
+      </c>
+      <c r="L19">
+        <v>963</v>
+      </c>
+      <c r="M19">
+        <v>767</v>
+      </c>
+      <c r="N19">
+        <v>659</v>
+      </c>
+      <c r="O19">
+        <v>610</v>
+      </c>
+      <c r="P19">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20">
+        <v>0.125</v>
+      </c>
+      <c r="F20">
+        <v>0.25</v>
+      </c>
+      <c r="G20">
+        <v>3552</v>
+      </c>
+      <c r="H20">
+        <v>3552</v>
+      </c>
+      <c r="I20">
+        <v>3552</v>
+      </c>
+      <c r="J20">
+        <v>2370</v>
+      </c>
+      <c r="K20">
+        <v>1716</v>
+      </c>
+      <c r="L20">
+        <v>1345</v>
+      </c>
+      <c r="M20">
+        <v>1135</v>
+      </c>
+      <c r="N20">
+        <v>1013</v>
+      </c>
+      <c r="O20">
+        <v>951</v>
+      </c>
+      <c r="P20">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21">
+        <v>0.125</v>
+      </c>
+      <c r="F21">
+        <v>0.31</v>
+      </c>
+      <c r="G21">
+        <v>1073</v>
+      </c>
+      <c r="H21">
+        <v>1073</v>
+      </c>
+      <c r="I21">
+        <v>1073</v>
+      </c>
+      <c r="J21">
+        <v>995</v>
+      </c>
+      <c r="K21">
+        <v>923</v>
+      </c>
+      <c r="L21">
+        <v>856</v>
+      </c>
+      <c r="M21">
+        <v>794</v>
+      </c>
+      <c r="N21">
+        <v>737</v>
+      </c>
+      <c r="O21">
+        <v>683</v>
+      </c>
+      <c r="P21">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22">
+        <v>0.125</v>
+      </c>
+      <c r="F22">
+        <v>0.73</v>
+      </c>
+      <c r="G22">
+        <v>2146</v>
+      </c>
+      <c r="H22">
+        <v>2146</v>
+      </c>
+      <c r="I22">
+        <v>2146</v>
+      </c>
+      <c r="J22">
+        <v>1991</v>
+      </c>
+      <c r="K22">
+        <v>1846</v>
+      </c>
+      <c r="L22">
+        <v>1713</v>
+      </c>
+      <c r="M22">
+        <v>1589</v>
+      </c>
+      <c r="N22">
+        <v>1474</v>
+      </c>
+      <c r="O22">
+        <v>1367</v>
+      </c>
+      <c r="P22">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23">
+        <v>0.125</v>
+      </c>
+      <c r="F23">
+        <v>0.9</v>
+      </c>
+      <c r="G23" s="2">
+        <v>521</v>
+      </c>
+      <c r="H23" s="2">
+        <v>521</v>
+      </c>
+      <c r="I23" s="2">
+        <v>521</v>
+      </c>
+      <c r="J23" s="2">
+        <v>485</v>
+      </c>
+      <c r="K23" s="2">
+        <v>448</v>
+      </c>
+      <c r="L23" s="2">
+        <v>421</v>
+      </c>
+      <c r="M23" s="2">
+        <v>406</v>
+      </c>
+      <c r="N23" s="2">
+        <v>391</v>
+      </c>
+      <c r="O23" s="2">
+        <v>376</v>
+      </c>
+      <c r="P23" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24">
+        <v>0.1</v>
+      </c>
+      <c r="F24">
+        <v>0.25</v>
+      </c>
+      <c r="G24">
+        <v>4403</v>
+      </c>
+      <c r="H24">
+        <v>4403</v>
+      </c>
+      <c r="I24">
+        <v>4403</v>
+      </c>
+      <c r="J24">
+        <v>2798</v>
+      </c>
+      <c r="K24">
+        <v>1946</v>
+      </c>
+      <c r="L24">
+        <v>1477</v>
+      </c>
+      <c r="M24">
+        <v>1192</v>
+      </c>
+      <c r="N24">
+        <v>1091</v>
+      </c>
+      <c r="O24">
+        <v>1024</v>
+      </c>
+      <c r="P24">
+        <v>1024</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="6.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2">
+        <v>1971</v>
+      </c>
+      <c r="G2">
+        <v>1990</v>
+      </c>
+      <c r="H2">
+        <v>2005</v>
+      </c>
+      <c r="I2">
+        <v>2020</v>
+      </c>
+      <c r="J2">
+        <v>2035</v>
+      </c>
+      <c r="K2">
+        <v>2050</v>
+      </c>
+      <c r="L2">
+        <v>2065</v>
+      </c>
+      <c r="M2">
+        <v>2080</v>
+      </c>
+      <c r="N2">
+        <v>2095</v>
+      </c>
+      <c r="O2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3">
+        <v>0.8</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.83</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8.83</v>
+      </c>
+      <c r="H3" s="3">
+        <v>8.83</v>
+      </c>
+      <c r="I3" s="3">
+        <v>8.83</v>
+      </c>
+      <c r="J3" s="3">
+        <v>8.31</v>
+      </c>
+      <c r="K3" s="3">
+        <v>7.83</v>
+      </c>
+      <c r="L3" s="3">
+        <v>7.37</v>
+      </c>
+      <c r="M3" s="3">
+        <v>6.94</v>
+      </c>
+      <c r="N3" s="3">
+        <v>6.54</v>
+      </c>
+      <c r="O3" s="3">
+        <f>N3</f>
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>0.8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="G4" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="H4" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="I4" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="J4" s="3">
+        <v>11.57</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10.42</v>
+      </c>
+      <c r="L4" s="3">
+        <v>10.36</v>
+      </c>
+      <c r="M4" s="3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="N4" s="3">
+        <v>9.92</v>
+      </c>
+      <c r="O4" s="3">
+        <f t="shared" ref="O4:O22" si="0">N4</f>
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <v>0.8</v>
+      </c>
+      <c r="F5" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="G5" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="H5" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="I5" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="J5" s="3">
+        <v>13.14</v>
+      </c>
+      <c r="K5" s="3">
+        <v>11.79</v>
+      </c>
+      <c r="L5" s="3">
+        <v>11.69</v>
+      </c>
+      <c r="M5" s="3">
+        <v>11.32</v>
+      </c>
+      <c r="N5" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="O5" s="3">
+        <f t="shared" si="0"/>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3.53</v>
+      </c>
+      <c r="K6" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3.13</v>
+      </c>
+      <c r="M6" s="3">
+        <v>2.95</v>
+      </c>
+      <c r="N6" s="3">
+        <v>2.78</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" si="0"/>
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.88</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.88</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3.88</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.88</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3.26</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3.21</v>
+      </c>
+      <c r="M7" s="3">
+        <v>3.13</v>
+      </c>
+      <c r="N7" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="O7" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="H8" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3.56</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3.41</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3.38</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" si="0"/>
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3.53</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3.13</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2.95</v>
+      </c>
+      <c r="N9" s="3">
+        <v>2.78</v>
+      </c>
+      <c r="O9" s="3">
+        <f t="shared" si="0"/>
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10">
+        <v>0.8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>11.16</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11.16</v>
+      </c>
+      <c r="H10" s="3">
+        <v>11.16</v>
+      </c>
+      <c r="I10" s="3">
+        <v>11.16</v>
+      </c>
+      <c r="J10" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K10" s="3">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="L10" s="3">
+        <v>9.24</v>
+      </c>
+      <c r="M10" s="3">
+        <v>9.01</v>
+      </c>
+      <c r="N10" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" si="0"/>
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="3">
+        <v>12.02</v>
+      </c>
+      <c r="G11" s="3">
+        <v>12.02</v>
+      </c>
+      <c r="H11" s="3">
+        <v>12.02</v>
+      </c>
+      <c r="I11" s="3">
+        <v>12.02</v>
+      </c>
+      <c r="J11" s="3">
+        <v>10.93</v>
+      </c>
+      <c r="K11" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="L11" s="3">
+        <v>9.86</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="N11" s="3">
+        <v>9.51</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="0"/>
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>9.09</v>
+      </c>
+      <c r="G12" s="3">
+        <v>9.09</v>
+      </c>
+      <c r="H12" s="3">
+        <v>9.09</v>
+      </c>
+      <c r="I12" s="3">
+        <v>9.09</v>
+      </c>
+      <c r="J12" s="3">
+        <v>8.56</v>
+      </c>
+      <c r="K12" s="3">
+        <v>8.06</v>
+      </c>
+      <c r="L12" s="3">
+        <v>7.59</v>
+      </c>
+      <c r="M12" s="3">
+        <v>7.15</v>
+      </c>
+      <c r="N12" s="3">
+        <v>6.73</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" si="0"/>
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="3">
+        <v>12.77</v>
+      </c>
+      <c r="G13" s="3">
+        <v>12.77</v>
+      </c>
+      <c r="H13" s="3">
+        <v>12.77</v>
+      </c>
+      <c r="I13" s="3">
+        <v>12.77</v>
+      </c>
+      <c r="J13" s="3">
+        <v>11.91</v>
+      </c>
+      <c r="K13" s="3">
+        <v>10.73</v>
+      </c>
+      <c r="L13" s="3">
+        <v>10.67</v>
+      </c>
+      <c r="M13" s="3">
+        <v>10.33</v>
+      </c>
+      <c r="N13" s="3">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="0"/>
+        <v>10.220000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="G14" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="H14" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="I14" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="J14" s="3">
+        <v>13.26</v>
+      </c>
+      <c r="K14" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="L14" s="3">
+        <v>11.81</v>
+      </c>
+      <c r="M14" s="3">
+        <v>11.44</v>
+      </c>
+      <c r="N14" s="3">
+        <v>11.31</v>
+      </c>
+      <c r="O14" s="3">
+        <f t="shared" si="0"/>
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15">
+        <v>0.9</v>
+      </c>
+      <c r="F15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="G15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="H15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="I15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="J15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="K15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="L15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="M15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="N15" s="3">
+        <v>22.02</v>
+      </c>
+      <c r="O15" s="3">
+        <v>22.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16">
+        <v>0.9</v>
+      </c>
+      <c r="F16" s="3">
+        <v>21.77</v>
+      </c>
+      <c r="G16" s="3">
+        <v>21.77</v>
+      </c>
+      <c r="H16" s="3">
+        <v>21.77</v>
+      </c>
+      <c r="I16" s="3">
+        <v>21.77</v>
+      </c>
+      <c r="J16" s="3">
+        <v>21.41</v>
+      </c>
+      <c r="K16" s="3">
+        <v>21.09</v>
+      </c>
+      <c r="L16" s="3">
+        <v>20.77</v>
+      </c>
+      <c r="M16" s="3">
+        <v>20.5</v>
+      </c>
+      <c r="N16" s="3">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" si="0"/>
+        <v>20.190000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17">
+        <v>0.45</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3.61</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.48</v>
+      </c>
+      <c r="L17" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3.22</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="0"/>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18">
+        <v>0.45</v>
+      </c>
+      <c r="F18" s="3">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="G18" s="3">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="H18" s="3">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="I18" s="3">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8.49</v>
+      </c>
+      <c r="K18" s="3">
+        <v>8.36</v>
+      </c>
+      <c r="L18" s="3">
+        <v>8.23</v>
+      </c>
+      <c r="M18" s="3">
+        <v>8.11</v>
+      </c>
+      <c r="N18" s="3">
+        <v>7.99</v>
+      </c>
+      <c r="O18" s="3">
+        <f t="shared" si="0"/>
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="G19" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="H19" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="I19" s="3">
+        <v>8.93</v>
+      </c>
+      <c r="J19" s="3">
+        <v>7.14</v>
+      </c>
+      <c r="K19" s="3">
+        <v>6.43</v>
+      </c>
+      <c r="L19" s="3">
+        <v>5.71</v>
+      </c>
+      <c r="M19" s="3">
+        <v>5.36</v>
+      </c>
+      <c r="N19" s="3">
+        <v>5.36</v>
+      </c>
+      <c r="O19" s="3">
+        <f t="shared" si="0"/>
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20">
+        <v>0.25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="G20" s="3">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="H20" s="3">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="I20" s="3">
+        <v>16.23</v>
+      </c>
+      <c r="J20" s="3">
+        <v>13.66</v>
+      </c>
+      <c r="K20" s="3">
+        <v>12.48</v>
+      </c>
+      <c r="L20" s="3">
+        <v>11.54</v>
+      </c>
+      <c r="M20" s="3">
+        <v>10.97</v>
+      </c>
+      <c r="N20" s="3">
+        <v>10.76</v>
+      </c>
+      <c r="O20" s="3">
+        <f t="shared" si="0"/>
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21">
+        <v>0.31</v>
+      </c>
+      <c r="F21" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="G21" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="H21" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="I21" s="3">
+        <v>15.42</v>
+      </c>
+      <c r="J21" s="3">
+        <v>14.3</v>
+      </c>
+      <c r="K21" s="3">
+        <v>13.26</v>
+      </c>
+      <c r="L21" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="M21" s="3">
+        <v>11.41</v>
+      </c>
+      <c r="N21" s="3">
+        <v>10.59</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="0"/>
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22">
+        <v>0.73</v>
+      </c>
+      <c r="F22" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="G22" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="H22" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="I22" s="3">
+        <v>15.42</v>
+      </c>
+      <c r="J22" s="3">
+        <v>14.3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>13.26</v>
+      </c>
+      <c r="L22" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>11.41</v>
+      </c>
+      <c r="N22" s="3">
+        <v>10.59</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" si="0"/>
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23">
+        <v>0.9</v>
+      </c>
+      <c r="F23" s="3">
+        <v>23.54</v>
+      </c>
+      <c r="G23" s="3">
+        <v>23.54</v>
+      </c>
+      <c r="H23" s="3">
+        <v>23.54</v>
+      </c>
+      <c r="I23" s="3">
+        <v>21.91</v>
+      </c>
+      <c r="J23" s="3">
+        <v>20.239999999999998</v>
+      </c>
+      <c r="K23" s="3">
+        <v>19.02</v>
+      </c>
+      <c r="L23" s="3">
+        <v>18.34</v>
+      </c>
+      <c r="M23" s="3">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="N23" s="3">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="O23" s="3">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24">
+        <v>0.25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>46.77</v>
+      </c>
+      <c r="G24" s="3">
+        <v>46.77</v>
+      </c>
+      <c r="H24" s="3">
+        <v>46.77</v>
+      </c>
+      <c r="I24" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="J24" s="3">
+        <v>17.3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>12.48</v>
+      </c>
+      <c r="L24" s="3">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
+        <v>7.69</v>
+      </c>
+      <c r="N24" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="O24" s="3">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -14512,7 +15060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15210,7 +15758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15382,7 +15930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15444,7 +15992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15530,7 +16078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15634,7 +16182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15768,7 +16316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15987,244 +16535,6 @@
       </c>
       <c r="M6" s="1">
         <v>1.5764652356959723</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12.1640625" customWidth="1"/>
-    <col min="2" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1971</v>
-      </c>
-      <c r="F2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1971</v>
-      </c>
-      <c r="E2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16529,6 +16839,244 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1971</v>
+      </c>
+      <c r="F2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1971</v>
+      </c>
+      <c r="E2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -16640,7 +17188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -16814,7 +17362,177 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -17197,7 +17915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -17835,7 +18553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -18471,7 +19189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -18769,7 +19487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -18899,687 +19617,6 @@
       </c>
       <c r="I5">
         <v>0.94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15">
-        <v>-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15">
-        <v>-6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19862,6 +19899,687 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15">
+        <v>-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15">
+        <v>-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -20132,7 +20850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -20523,7 +21241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -20877,7 +21595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="32140" windowHeight="21340" tabRatio="684" firstSheet="43" activeTab="43"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15960" tabRatio="684" firstSheet="26" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -756,8 +756,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1685">
+  <cellStyleXfs count="1699">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2451,7 +2465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1685">
+  <cellStyles count="1699">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3294,6 +3308,13 @@
     <cellStyle name="Followed Hyperlink" xfId="1680" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1682" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1684" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1686" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1688" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1690" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1692" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1694" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1696" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1698" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -4136,6 +4157,13 @@
     <cellStyle name="Hyperlink" xfId="1679" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1681" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1683" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1685" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1687" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1689" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1691" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1693" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1695" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1697" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15960" tabRatio="684" firstSheet="26" activeTab="27"/>
+    <workbookView xWindow="22720" yWindow="1240" windowWidth="24980" windowHeight="16240" tabRatio="684" firstSheet="14" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -22,47 +22,48 @@
     <sheet name="A22.subsector_logit.csv" sheetId="25" r:id="rId13"/>
     <sheet name="A22.subsector_shrwt.csv" sheetId="8" r:id="rId14"/>
     <sheet name="A22.subsector_interp.csv" sheetId="26" r:id="rId15"/>
-    <sheet name="A22.globaltech_cost.csv" sheetId="27" r:id="rId16"/>
-    <sheet name="A22.globaltech_coef.csv" sheetId="3" r:id="rId17"/>
-    <sheet name="A22.globaltech_shrwt.csv" sheetId="29" r:id="rId18"/>
-    <sheet name="A22.globaltech_retirement.csv" sheetId="28" r:id="rId19"/>
-    <sheet name="A22.globaltech_co2capture.csv" sheetId="30" r:id="rId20"/>
-    <sheet name="A23.sector.csv" sheetId="35" r:id="rId21"/>
-    <sheet name="A23.subsector_logit.csv" sheetId="37" r:id="rId22"/>
-    <sheet name="A23.subsector_shrwt.csv" sheetId="38" r:id="rId23"/>
-    <sheet name="A23.subsector_interp.csv" sheetId="39" r:id="rId24"/>
-    <sheet name="A23.chp_elecratio.csv" sheetId="42" r:id="rId25"/>
-    <sheet name="A23.globalinttech.csv" sheetId="49" r:id="rId26"/>
-    <sheet name="A23.globaltech_shrwt.csv" sheetId="45" r:id="rId27"/>
-    <sheet name="A23.globaltech_keyword.csv" sheetId="69" r:id="rId28"/>
-    <sheet name="A23.globaltech_eff.csv" sheetId="43" r:id="rId29"/>
-    <sheet name="A23.globaltech_capital.csv" sheetId="46" r:id="rId30"/>
-    <sheet name="A23.globaltech_OMfixed.csv" sheetId="47" r:id="rId31"/>
-    <sheet name="A23.globaltech_OMvar.csv" sheetId="44" r:id="rId32"/>
-    <sheet name="A23.globaltech_retirement.csv" sheetId="48" r:id="rId33"/>
-    <sheet name="A23.globaltech_co2capture.csv" sheetId="50" r:id="rId34"/>
-    <sheet name="A24.sector.csv" sheetId="53" r:id="rId35"/>
-    <sheet name="A24.subsector_logit.csv" sheetId="54" r:id="rId36"/>
-    <sheet name="A24.subsector_shrwt.csv" sheetId="55" r:id="rId37"/>
-    <sheet name="A24.subsector_interp.csv" sheetId="56" r:id="rId38"/>
-    <sheet name="A24.globaltech_cost.csv" sheetId="57" r:id="rId39"/>
-    <sheet name="A24.globaltech_coef.csv" sheetId="58" r:id="rId40"/>
-    <sheet name="A24.globaltech_shrwt.csv" sheetId="59" r:id="rId41"/>
-    <sheet name="A25.sector.csv" sheetId="60" r:id="rId42"/>
-    <sheet name="A25.subsector_logit.csv" sheetId="61" r:id="rId43"/>
-    <sheet name="A25.globaltech_keyword.csv" sheetId="71" r:id="rId44"/>
-    <sheet name="A25.subsector_shrwt.csv" sheetId="62" r:id="rId45"/>
-    <sheet name="A25.globaltech_cost.csv" sheetId="64" r:id="rId46"/>
-    <sheet name="A25.globaltech_eff.csv" sheetId="65" r:id="rId47"/>
-    <sheet name="A25.globaltech_shrwt.csv" sheetId="66" r:id="rId48"/>
-    <sheet name="A25.globaltech_co2capture.csv" sheetId="67" r:id="rId49"/>
-    <sheet name="A26.sector.csv" sheetId="6" r:id="rId50"/>
-    <sheet name="A26.subsector_logit.csv" sheetId="32" r:id="rId51"/>
-    <sheet name="A26.subsector_shrwt.csv" sheetId="33" r:id="rId52"/>
-    <sheet name="A26.subsector_interp.csv" sheetId="51" r:id="rId53"/>
-    <sheet name="A26.globaltech_cost.csv" sheetId="31" r:id="rId54"/>
-    <sheet name="A26.globaltech_eff.csv" sheetId="7" r:id="rId55"/>
-    <sheet name="A26.globaltech_shrwt.csv" sheetId="52" r:id="rId56"/>
+    <sheet name="A22.globaltech_interp.csv" sheetId="72" r:id="rId16"/>
+    <sheet name="A22.globaltech_cost.csv" sheetId="27" r:id="rId17"/>
+    <sheet name="A22.globaltech_coef.csv" sheetId="3" r:id="rId18"/>
+    <sheet name="A22.globaltech_shrwt.csv" sheetId="29" r:id="rId19"/>
+    <sheet name="A22.globaltech_retirement.csv" sheetId="28" r:id="rId20"/>
+    <sheet name="A22.globaltech_co2capture.csv" sheetId="30" r:id="rId21"/>
+    <sheet name="A23.sector.csv" sheetId="35" r:id="rId22"/>
+    <sheet name="A23.subsector_logit.csv" sheetId="37" r:id="rId23"/>
+    <sheet name="A23.subsector_shrwt.csv" sheetId="38" r:id="rId24"/>
+    <sheet name="A23.subsector_interp.csv" sheetId="39" r:id="rId25"/>
+    <sheet name="A23.chp_elecratio.csv" sheetId="42" r:id="rId26"/>
+    <sheet name="A23.globalinttech.csv" sheetId="49" r:id="rId27"/>
+    <sheet name="A23.globaltech_shrwt.csv" sheetId="45" r:id="rId28"/>
+    <sheet name="A23.globaltech_keyword.csv" sheetId="69" r:id="rId29"/>
+    <sheet name="A23.globaltech_eff.csv" sheetId="43" r:id="rId30"/>
+    <sheet name="A23.globaltech_capital.csv" sheetId="46" r:id="rId31"/>
+    <sheet name="A23.globaltech_OMfixed.csv" sheetId="47" r:id="rId32"/>
+    <sheet name="A23.globaltech_OMvar.csv" sheetId="44" r:id="rId33"/>
+    <sheet name="A23.globaltech_retirement.csv" sheetId="48" r:id="rId34"/>
+    <sheet name="A23.globaltech_co2capture.csv" sheetId="50" r:id="rId35"/>
+    <sheet name="A24.sector.csv" sheetId="53" r:id="rId36"/>
+    <sheet name="A24.subsector_logit.csv" sheetId="54" r:id="rId37"/>
+    <sheet name="A24.subsector_shrwt.csv" sheetId="55" r:id="rId38"/>
+    <sheet name="A24.subsector_interp.csv" sheetId="56" r:id="rId39"/>
+    <sheet name="A24.globaltech_cost.csv" sheetId="57" r:id="rId40"/>
+    <sheet name="A24.globaltech_coef.csv" sheetId="58" r:id="rId41"/>
+    <sheet name="A24.globaltech_shrwt.csv" sheetId="59" r:id="rId42"/>
+    <sheet name="A25.sector.csv" sheetId="60" r:id="rId43"/>
+    <sheet name="A25.subsector_logit.csv" sheetId="61" r:id="rId44"/>
+    <sheet name="A25.globaltech_keyword.csv" sheetId="71" r:id="rId45"/>
+    <sheet name="A25.subsector_shrwt.csv" sheetId="62" r:id="rId46"/>
+    <sheet name="A25.globaltech_cost.csv" sheetId="64" r:id="rId47"/>
+    <sheet name="A25.globaltech_eff.csv" sheetId="65" r:id="rId48"/>
+    <sheet name="A25.globaltech_shrwt.csv" sheetId="66" r:id="rId49"/>
+    <sheet name="A25.globaltech_co2capture.csv" sheetId="67" r:id="rId50"/>
+    <sheet name="A26.sector.csv" sheetId="6" r:id="rId51"/>
+    <sheet name="A26.subsector_logit.csv" sheetId="32" r:id="rId52"/>
+    <sheet name="A26.subsector_shrwt.csv" sheetId="33" r:id="rId53"/>
+    <sheet name="A26.subsector_interp.csv" sheetId="51" r:id="rId54"/>
+    <sheet name="A26.globaltech_cost.csv" sheetId="31" r:id="rId55"/>
+    <sheet name="A26.globaltech_eff.csv" sheetId="7" r:id="rId56"/>
+    <sheet name="A26.globaltech_shrwt.csv" sheetId="52" r:id="rId57"/>
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="209">
   <si>
     <t>technology</t>
   </si>
@@ -699,6 +700,9 @@
   <si>
     <t># Hydrogen technology keywords</t>
   </si>
+  <si>
+    <t># Primary energy transformation technology interpolation (for techs that may have cal values in subsectors with multiple calibrated technologies)</t>
+  </si>
 </sst>
 </file>
 
@@ -756,8 +760,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1699">
+  <cellStyleXfs count="1709">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2465,7 +2479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1699">
+  <cellStyles count="1709">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3315,6 +3329,11 @@
     <cellStyle name="Followed Hyperlink" xfId="1694" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1696" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1698" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1700" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1702" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1704" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1706" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1708" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -4164,6 +4183,11 @@
     <cellStyle name="Hyperlink" xfId="1693" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1695" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1697" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1699" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1701" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1703" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1705" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1707" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5111,7 +5135,7 @@
         <v>43</v>
       </c>
       <c r="C9">
-        <v>-13</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5122,7 +5146,7 @@
         <v>45</v>
       </c>
       <c r="C10">
-        <v>-13</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5555,6 +5579,170 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3">
+        <v>2020</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4">
+        <v>2020</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -6043,7 +6231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -6168,16 +6356,13 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:G7" si="0">1/421.377</f>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
       <c r="F6">
-        <f>1/421.377</f>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
       <c r="G6">
-        <f>1/421.377</f>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -6194,16 +6379,13 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
-        <v>2.3731717677993817E-3</v>
+        <v>2.3731720000000002E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -6311,17 +6493,14 @@
       <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="1">
-        <f>E11*1.04</f>
-        <v>2.1964800000000002</v>
-      </c>
-      <c r="F12" s="1">
-        <f t="shared" ref="F12:G12" si="1">F11*1.04</f>
-        <v>2.1964800000000002</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="1"/>
-        <v>2.0373600000000001</v>
+      <c r="E12">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="F12">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="G12">
+        <v>2.0369999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6337,17 +6516,14 @@
       <c r="D13" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="1">
-        <f>E11*1.1</f>
-        <v>2.3232000000000004</v>
-      </c>
-      <c r="F13" s="1">
-        <f t="shared" ref="F13:G13" si="2">F11*1.1</f>
-        <v>2.3232000000000004</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="2"/>
-        <v>2.1549</v>
+      <c r="E13">
+        <v>2.323</v>
+      </c>
+      <c r="F13">
+        <v>2.323</v>
+      </c>
+      <c r="G13">
+        <v>2.1549999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6409,17 +6585,14 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="1">
-        <f>E15*1.04</f>
-        <v>2.1392799999999998</v>
-      </c>
-      <c r="F16" s="1">
-        <f t="shared" ref="F16" si="3">F15*1.04</f>
-        <v>2.1392799999999998</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" ref="G16" si="4">G15*1.04</f>
-        <v>1.8418399999999999</v>
+      <c r="E16">
+        <v>2.1389999999999998</v>
+      </c>
+      <c r="F16">
+        <v>2.1389999999999998</v>
+      </c>
+      <c r="G16">
+        <v>1.8420000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6435,17 +6608,14 @@
       <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="1">
-        <f>E15*1.1</f>
-        <v>2.2627000000000002</v>
-      </c>
-      <c r="F17" s="1">
-        <f t="shared" ref="F17:G17" si="5">F15*1.1</f>
-        <v>2.2627000000000002</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" si="5"/>
-        <v>1.9481000000000002</v>
+      <c r="E17">
+        <v>2.2629999999999999</v>
+      </c>
+      <c r="F17">
+        <v>2.2629999999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.948</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -6484,17 +6654,14 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="1">
-        <f>E18*1.04</f>
-        <v>2.0394400000000004</v>
-      </c>
-      <c r="F19" s="1">
-        <f t="shared" ref="F19" si="6">F18*1.04</f>
-        <v>2.0394400000000004</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" ref="G19" si="7">G18*1.04</f>
-        <v>1.8085600000000002</v>
+      <c r="E19">
+        <v>2.0390000000000001</v>
+      </c>
+      <c r="F19">
+        <v>2.0390000000000001</v>
+      </c>
+      <c r="G19">
+        <v>1.8089999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6510,17 +6677,14 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="1">
-        <f>E18*1.1</f>
-        <v>2.1571000000000002</v>
-      </c>
-      <c r="F20" s="1">
-        <f t="shared" ref="F20:G20" si="8">F18*1.1</f>
-        <v>2.1571000000000002</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="8"/>
-        <v>1.9129000000000003</v>
+      <c r="E20">
+        <v>2.157</v>
+      </c>
+      <c r="F20">
+        <v>2.157</v>
+      </c>
+      <c r="G20">
+        <v>1.913</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -6672,7 +6836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -7208,709 +7372,6 @@
       </c>
       <c r="H21">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3">
-        <v>45</v>
-      </c>
-      <c r="F3">
-        <v>0.05</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4">
-        <v>45</v>
-      </c>
-      <c r="F4">
-        <v>0.05</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5">
-        <v>45</v>
-      </c>
-      <c r="F5">
-        <v>0.05</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>45</v>
-      </c>
-      <c r="F6">
-        <v>0.05</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7">
-        <v>45</v>
-      </c>
-      <c r="F7">
-        <v>0.05</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>0.05</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9">
-        <v>45</v>
-      </c>
-      <c r="F9">
-        <v>0.05</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>0.05</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11">
-        <v>45</v>
-      </c>
-      <c r="F11">
-        <v>0.05</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12">
-        <v>45</v>
-      </c>
-      <c r="F12">
-        <v>0.05</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13">
-        <v>45</v>
-      </c>
-      <c r="F13">
-        <v>0.05</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14">
-        <v>45</v>
-      </c>
-      <c r="F14">
-        <v>0.05</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>0.05</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16">
-        <v>45</v>
-      </c>
-      <c r="F16">
-        <v>0.05</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17">
-        <v>45</v>
-      </c>
-      <c r="F17">
-        <v>0.03</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18">
-        <v>45</v>
-      </c>
-      <c r="F18">
-        <v>0.03</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19">
-        <v>45</v>
-      </c>
-      <c r="F19">
-        <v>0.03</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20">
-        <v>45</v>
-      </c>
-      <c r="F20">
-        <v>0.03</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21">
-        <v>45</v>
-      </c>
-      <c r="F21">
-        <v>0.03</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22">
-        <v>45</v>
-      </c>
-      <c r="F22">
-        <v>0.03</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23">
-        <v>45</v>
-      </c>
-      <c r="F23">
-        <v>0.03</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>0.03</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25">
-        <v>45</v>
-      </c>
-      <c r="F25">
-        <v>0.03</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26">
-        <v>45</v>
-      </c>
-      <c r="F26">
-        <v>0.03</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27">
-        <v>45</v>
-      </c>
-      <c r="F27">
-        <v>0.03</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28">
-        <v>45</v>
-      </c>
-      <c r="F28">
-        <v>0.03</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29">
-        <v>45</v>
-      </c>
-      <c r="F29">
-        <v>0.03</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30">
-        <v>45</v>
-      </c>
-      <c r="F30">
-        <v>0.03</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8106,6 +7567,709 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>0.05</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>0.05</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>0.05</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>45</v>
+      </c>
+      <c r="F6">
+        <v>0.05</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>0.05</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>0.05</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>0.05</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>0.05</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>0.05</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>0.05</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>0.05</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>0.05</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>0.05</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16">
+        <v>45</v>
+      </c>
+      <c r="F16">
+        <v>0.05</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>0.03</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18">
+        <v>45</v>
+      </c>
+      <c r="F18">
+        <v>0.03</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19">
+        <v>45</v>
+      </c>
+      <c r="F19">
+        <v>0.03</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20">
+        <v>45</v>
+      </c>
+      <c r="F20">
+        <v>0.03</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>0.03</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>0.03</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>0.03</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>0.03</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25">
+        <v>45</v>
+      </c>
+      <c r="F25">
+        <v>0.03</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>0.03</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27">
+        <v>45</v>
+      </c>
+      <c r="F27">
+        <v>0.03</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28">
+        <v>45</v>
+      </c>
+      <c r="F28">
+        <v>0.03</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>0.03</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30">
+        <v>45</v>
+      </c>
+      <c r="F30">
+        <v>0.03</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -8250,7 +8414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8347,7 +8511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8499,7 +8663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -8700,7 +8864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -9034,7 +9198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -9092,7 +9256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -9283,7 +9447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -10152,7 +10316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -10505,1256 +10669,6 @@
       </c>
       <c r="D25" t="s">
         <v>202</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12.1640625" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1971</v>
-      </c>
-      <c r="F2">
-        <v>1990</v>
-      </c>
-      <c r="G2">
-        <v>2005</v>
-      </c>
-      <c r="H2">
-        <v>2010</v>
-      </c>
-      <c r="I2">
-        <v>2015</v>
-      </c>
-      <c r="J2">
-        <v>2020</v>
-      </c>
-      <c r="K2">
-        <v>2035</v>
-      </c>
-      <c r="L2">
-        <v>2050</v>
-      </c>
-      <c r="M2">
-        <v>2065</v>
-      </c>
-      <c r="N2">
-        <v>2080</v>
-      </c>
-      <c r="O2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>0.3</v>
-      </c>
-      <c r="F3">
-        <v>0.35</v>
-      </c>
-      <c r="G3">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="H3">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="I3">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="J3">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="K3">
-        <v>0.4</v>
-      </c>
-      <c r="L3">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="M3">
-        <v>0.41899999999999998</v>
-      </c>
-      <c r="N3">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="O3">
-        <v>0.438</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="F4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="G4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="H4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="I4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="J4">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="K4">
-        <v>0.44900000000000001</v>
-      </c>
-      <c r="L4">
-        <v>0.47</v>
-      </c>
-      <c r="M4">
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="N4">
-        <v>0.496</v>
-      </c>
-      <c r="O4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>0.35632932299999998</v>
-      </c>
-      <c r="F5">
-        <v>0.35632932299999998</v>
-      </c>
-      <c r="G5">
-        <v>0.35632932299999998</v>
-      </c>
-      <c r="H5">
-        <v>0.35632932299999998</v>
-      </c>
-      <c r="I5">
-        <v>0.35632932299999998</v>
-      </c>
-      <c r="J5">
-        <v>0.36428907700000002</v>
-      </c>
-      <c r="K5">
-        <v>0.394133281</v>
-      </c>
-      <c r="L5">
-        <v>0.42094357999999998</v>
-      </c>
-      <c r="M5">
-        <v>0.43725985699999997</v>
-      </c>
-      <c r="N5">
-        <v>0.44773555100000001</v>
-      </c>
-      <c r="O5">
-        <v>0.45134522900000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>0.25</v>
-      </c>
-      <c r="F6">
-        <v>0.3</v>
-      </c>
-      <c r="G6">
-        <v>0.33</v>
-      </c>
-      <c r="H6">
-        <v>0.33</v>
-      </c>
-      <c r="I6">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="J6">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="K6">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="L6">
-        <v>0.40200000000000002</v>
-      </c>
-      <c r="M6">
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="N6">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="O6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>0.45</v>
-      </c>
-      <c r="F7">
-        <v>0.45</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I7">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="J7">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="K7">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="L7">
-        <v>0.64</v>
-      </c>
-      <c r="M7">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="N7">
-        <v>0.69299999999999995</v>
-      </c>
-      <c r="O7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>0.48720148200000002</v>
-      </c>
-      <c r="F8">
-        <v>0.48720148200000002</v>
-      </c>
-      <c r="G8">
-        <v>0.48720148200000002</v>
-      </c>
-      <c r="H8">
-        <v>0.48720148200000002</v>
-      </c>
-      <c r="I8">
-        <v>0.48720148200000002</v>
-      </c>
-      <c r="J8">
-        <v>0.49097364900000001</v>
-      </c>
-      <c r="K8">
-        <v>0.53978271600000005</v>
-      </c>
-      <c r="L8">
-        <v>0.58396003900000004</v>
-      </c>
-      <c r="M8">
-        <v>0.61635640599999997</v>
-      </c>
-      <c r="N8">
-        <v>0.63715615400000003</v>
-      </c>
-      <c r="O8">
-        <v>0.64432325899999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9">
-        <v>0.3</v>
-      </c>
-      <c r="F9">
-        <v>0.35</v>
-      </c>
-      <c r="G9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="H9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="I9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="J9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="K9">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="L9">
-        <v>0.40200000000000002</v>
-      </c>
-      <c r="M9">
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="N9">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="O9">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="F10">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="G10">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="H10">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="I10">
-        <v>0.42624803</v>
-      </c>
-      <c r="J10">
-        <v>0.42624803</v>
-      </c>
-      <c r="K10">
-        <v>0.44903864199999999</v>
-      </c>
-      <c r="L10">
-        <v>0.46959835</v>
-      </c>
-      <c r="M10">
-        <v>0.48591462699999999</v>
-      </c>
-      <c r="N10">
-        <v>0.49639032199999999</v>
-      </c>
-      <c r="O10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.35983912000000001</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.35983912000000001</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.35983912000000001</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0.35983912000000001</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.35983912000000001</v>
-      </c>
-      <c r="J11">
-        <v>0.363613943</v>
-      </c>
-      <c r="K11">
-        <v>0.38996481</v>
-      </c>
-      <c r="L11">
-        <v>0.41388239999999998</v>
-      </c>
-      <c r="M11">
-        <v>0.43019867699999997</v>
-      </c>
-      <c r="N11">
-        <v>0.44067437199999998</v>
-      </c>
-      <c r="O11">
-        <v>0.44428404999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-      <c r="F12">
-        <v>0.35</v>
-      </c>
-      <c r="G12">
-        <v>0.38200000000000001</v>
-      </c>
-      <c r="H12">
-        <v>0.38200000000000001</v>
-      </c>
-      <c r="I12">
-        <v>0.38200000000000001</v>
-      </c>
-      <c r="J12">
-        <v>0.38200000000000001</v>
-      </c>
-      <c r="K12">
-        <v>0.39</v>
-      </c>
-      <c r="L12">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="M12">
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="N12">
-        <v>0.41799999999999998</v>
-      </c>
-      <c r="O12">
-        <v>0.42699999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="F13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="G13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="H13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="I13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="J13">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="K13">
-        <v>0.438</v>
-      </c>
-      <c r="L13">
-        <v>0.45800000000000002</v>
-      </c>
-      <c r="M13">
-        <v>0.47399999999999998</v>
-      </c>
-      <c r="N13">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="O13">
-        <v>0.48799999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14">
-        <v>0.35685245700000001</v>
-      </c>
-      <c r="F14">
-        <v>0.35685245700000001</v>
-      </c>
-      <c r="G14">
-        <v>0.35685245700000001</v>
-      </c>
-      <c r="H14">
-        <v>0.35685245700000001</v>
-      </c>
-      <c r="I14">
-        <v>0.35685245700000001</v>
-      </c>
-      <c r="J14">
-        <v>0.36355847699999999</v>
-      </c>
-      <c r="K14">
-        <v>0.39173081300000001</v>
-      </c>
-      <c r="L14">
-        <v>0.41705062399999998</v>
-      </c>
-      <c r="M14">
-        <v>0.43296536699999999</v>
-      </c>
-      <c r="N14">
-        <v>0.44318326200000002</v>
-      </c>
-      <c r="O14">
-        <v>0.44670410799999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="F15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="G15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="I15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="J15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="K15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="L15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="M15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="N15">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="O15">
-        <v>0.33300000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="F16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="G16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="I16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="J16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="K16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="L16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="M16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="N16">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="O16">
-        <v>0.33300000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18">
-        <v>0.96</v>
-      </c>
-      <c r="F18">
-        <v>0.96</v>
-      </c>
-      <c r="G18">
-        <v>0.96</v>
-      </c>
-      <c r="H18">
-        <v>0.96</v>
-      </c>
-      <c r="I18">
-        <v>0.96</v>
-      </c>
-      <c r="J18">
-        <v>0.96</v>
-      </c>
-      <c r="K18">
-        <v>0.96</v>
-      </c>
-      <c r="L18">
-        <v>0.96</v>
-      </c>
-      <c r="M18">
-        <v>0.96</v>
-      </c>
-      <c r="N18">
-        <v>0.96</v>
-      </c>
-      <c r="O18">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21">
-        <v>0.96</v>
-      </c>
-      <c r="F21">
-        <v>0.96</v>
-      </c>
-      <c r="G21">
-        <v>0.96</v>
-      </c>
-      <c r="H21">
-        <v>0.96</v>
-      </c>
-      <c r="I21">
-        <v>0.96</v>
-      </c>
-      <c r="J21">
-        <v>0.96</v>
-      </c>
-      <c r="K21">
-        <v>0.96</v>
-      </c>
-      <c r="L21">
-        <v>0.96</v>
-      </c>
-      <c r="M21">
-        <v>0.96</v>
-      </c>
-      <c r="N21">
-        <v>0.96</v>
-      </c>
-      <c r="O21">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25">
-        <v>0.1</v>
-      </c>
-      <c r="F25">
-        <v>0.1</v>
-      </c>
-      <c r="G25">
-        <v>0.1</v>
-      </c>
-      <c r="H25">
-        <v>0.1</v>
-      </c>
-      <c r="I25">
-        <v>0.1</v>
-      </c>
-      <c r="J25">
-        <v>0.1</v>
-      </c>
-      <c r="K25">
-        <v>0.1</v>
-      </c>
-      <c r="L25">
-        <v>0.1</v>
-      </c>
-      <c r="M25">
-        <v>0.1</v>
-      </c>
-      <c r="N25">
-        <v>0.1</v>
-      </c>
-      <c r="O25">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11988,6 +10902,1256 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1971</v>
+      </c>
+      <c r="F2">
+        <v>1990</v>
+      </c>
+      <c r="G2">
+        <v>2005</v>
+      </c>
+      <c r="H2">
+        <v>2010</v>
+      </c>
+      <c r="I2">
+        <v>2015</v>
+      </c>
+      <c r="J2">
+        <v>2020</v>
+      </c>
+      <c r="K2">
+        <v>2035</v>
+      </c>
+      <c r="L2">
+        <v>2050</v>
+      </c>
+      <c r="M2">
+        <v>2065</v>
+      </c>
+      <c r="N2">
+        <v>2080</v>
+      </c>
+      <c r="O2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>0.3</v>
+      </c>
+      <c r="F3">
+        <v>0.35</v>
+      </c>
+      <c r="G3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="H3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K3">
+        <v>0.4</v>
+      </c>
+      <c r="L3">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="M3">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="N3">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="O3">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="G4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="H4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="J4">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="K4">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.47</v>
+      </c>
+      <c r="M4">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="N4">
+        <v>0.496</v>
+      </c>
+      <c r="O4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>0.35632932299999998</v>
+      </c>
+      <c r="F5">
+        <v>0.35632932299999998</v>
+      </c>
+      <c r="G5">
+        <v>0.35632932299999998</v>
+      </c>
+      <c r="H5">
+        <v>0.35632932299999998</v>
+      </c>
+      <c r="I5">
+        <v>0.35632932299999998</v>
+      </c>
+      <c r="J5">
+        <v>0.36428907700000002</v>
+      </c>
+      <c r="K5">
+        <v>0.394133281</v>
+      </c>
+      <c r="L5">
+        <v>0.42094357999999998</v>
+      </c>
+      <c r="M5">
+        <v>0.43725985699999997</v>
+      </c>
+      <c r="N5">
+        <v>0.44773555100000001</v>
+      </c>
+      <c r="O5">
+        <v>0.45134522900000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>0.25</v>
+      </c>
+      <c r="F6">
+        <v>0.3</v>
+      </c>
+      <c r="G6">
+        <v>0.33</v>
+      </c>
+      <c r="H6">
+        <v>0.33</v>
+      </c>
+      <c r="I6">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="J6">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="K6">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="L6">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="M6">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="N6">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="O6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>0.45</v>
+      </c>
+      <c r="F7">
+        <v>0.45</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I7">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="J7">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="K7">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="L7">
+        <v>0.64</v>
+      </c>
+      <c r="M7">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="N7">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="O7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>0.48720148200000002</v>
+      </c>
+      <c r="F8">
+        <v>0.48720148200000002</v>
+      </c>
+      <c r="G8">
+        <v>0.48720148200000002</v>
+      </c>
+      <c r="H8">
+        <v>0.48720148200000002</v>
+      </c>
+      <c r="I8">
+        <v>0.48720148200000002</v>
+      </c>
+      <c r="J8">
+        <v>0.49097364900000001</v>
+      </c>
+      <c r="K8">
+        <v>0.53978271600000005</v>
+      </c>
+      <c r="L8">
+        <v>0.58396003900000004</v>
+      </c>
+      <c r="M8">
+        <v>0.61635640599999997</v>
+      </c>
+      <c r="N8">
+        <v>0.63715615400000003</v>
+      </c>
+      <c r="O8">
+        <v>0.64432325899999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9">
+        <v>0.3</v>
+      </c>
+      <c r="F9">
+        <v>0.35</v>
+      </c>
+      <c r="G9">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="J9">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="K9">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="L9">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="M9">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="N9">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="O9">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="F10">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="G10">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="H10">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.42624803</v>
+      </c>
+      <c r="J10">
+        <v>0.42624803</v>
+      </c>
+      <c r="K10">
+        <v>0.44903864199999999</v>
+      </c>
+      <c r="L10">
+        <v>0.46959835</v>
+      </c>
+      <c r="M10">
+        <v>0.48591462699999999</v>
+      </c>
+      <c r="N10">
+        <v>0.49639032199999999</v>
+      </c>
+      <c r="O10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.35983912000000001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.35983912000000001</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.35983912000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.35983912000000001</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.35983912000000001</v>
+      </c>
+      <c r="J11">
+        <v>0.363613943</v>
+      </c>
+      <c r="K11">
+        <v>0.38996481</v>
+      </c>
+      <c r="L11">
+        <v>0.41388239999999998</v>
+      </c>
+      <c r="M11">
+        <v>0.43019867699999997</v>
+      </c>
+      <c r="N11">
+        <v>0.44067437199999998</v>
+      </c>
+      <c r="O11">
+        <v>0.44428404999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>0.3</v>
+      </c>
+      <c r="F12">
+        <v>0.35</v>
+      </c>
+      <c r="G12">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="H12">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="J12">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="K12">
+        <v>0.39</v>
+      </c>
+      <c r="L12">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="M12">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="N12">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="O12">
+        <v>0.42699999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="F13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="G13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="H13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="I13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="J13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="K13">
+        <v>0.438</v>
+      </c>
+      <c r="L13">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="M13">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="N13">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="O13">
+        <v>0.48799999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14">
+        <v>0.35685245700000001</v>
+      </c>
+      <c r="F14">
+        <v>0.35685245700000001</v>
+      </c>
+      <c r="G14">
+        <v>0.35685245700000001</v>
+      </c>
+      <c r="H14">
+        <v>0.35685245700000001</v>
+      </c>
+      <c r="I14">
+        <v>0.35685245700000001</v>
+      </c>
+      <c r="J14">
+        <v>0.36355847699999999</v>
+      </c>
+      <c r="K14">
+        <v>0.39173081300000001</v>
+      </c>
+      <c r="L14">
+        <v>0.41705062399999998</v>
+      </c>
+      <c r="M14">
+        <v>0.43296536699999999</v>
+      </c>
+      <c r="N14">
+        <v>0.44318326200000002</v>
+      </c>
+      <c r="O14">
+        <v>0.44670410799999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="F15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="G15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="H15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="M15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="N15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="O15">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="F16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="G16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="H16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="M16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="N16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="O16">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18">
+        <v>0.96</v>
+      </c>
+      <c r="F18">
+        <v>0.96</v>
+      </c>
+      <c r="G18">
+        <v>0.96</v>
+      </c>
+      <c r="H18">
+        <v>0.96</v>
+      </c>
+      <c r="I18">
+        <v>0.96</v>
+      </c>
+      <c r="J18">
+        <v>0.96</v>
+      </c>
+      <c r="K18">
+        <v>0.96</v>
+      </c>
+      <c r="L18">
+        <v>0.96</v>
+      </c>
+      <c r="M18">
+        <v>0.96</v>
+      </c>
+      <c r="N18">
+        <v>0.96</v>
+      </c>
+      <c r="O18">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21">
+        <v>0.96</v>
+      </c>
+      <c r="F21">
+        <v>0.96</v>
+      </c>
+      <c r="G21">
+        <v>0.96</v>
+      </c>
+      <c r="H21">
+        <v>0.96</v>
+      </c>
+      <c r="I21">
+        <v>0.96</v>
+      </c>
+      <c r="J21">
+        <v>0.96</v>
+      </c>
+      <c r="K21">
+        <v>0.96</v>
+      </c>
+      <c r="L21">
+        <v>0.96</v>
+      </c>
+      <c r="M21">
+        <v>0.96</v>
+      </c>
+      <c r="N21">
+        <v>0.96</v>
+      </c>
+      <c r="O21">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25">
+        <v>0.1</v>
+      </c>
+      <c r="F25">
+        <v>0.1</v>
+      </c>
+      <c r="G25">
+        <v>0.1</v>
+      </c>
+      <c r="H25">
+        <v>0.1</v>
+      </c>
+      <c r="I25">
+        <v>0.1</v>
+      </c>
+      <c r="J25">
+        <v>0.1</v>
+      </c>
+      <c r="K25">
+        <v>0.1</v>
+      </c>
+      <c r="L25">
+        <v>0.1</v>
+      </c>
+      <c r="M25">
+        <v>0.1</v>
+      </c>
+      <c r="N25">
+        <v>0.1</v>
+      </c>
+      <c r="O25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -13167,7 +13331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -14296,7 +14460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15088,7 +15252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15786,7 +15950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -15958,7 +16122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -16020,7 +16184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -16106,7 +16270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -16210,7 +16374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -16331,238 +16495,6 @@
       </c>
       <c r="G6" t="s">
         <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="5.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2">
-        <v>1971</v>
-      </c>
-      <c r="F2">
-        <v>2005</v>
-      </c>
-      <c r="G2">
-        <v>2020</v>
-      </c>
-      <c r="H2">
-        <v>2035</v>
-      </c>
-      <c r="I2">
-        <v>2050</v>
-      </c>
-      <c r="J2">
-        <v>2065</v>
-      </c>
-      <c r="K2">
-        <v>2080</v>
-      </c>
-      <c r="L2">
-        <v>2095</v>
-      </c>
-      <c r="M2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.7094391110222915</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1.7094391110222915</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.7094391110222915</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.6096954353251778</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.5157716807808108</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.4273282621273939</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1.3440454084866928</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1.2656220072190574</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1.2656220072190574</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.71012653542365767</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.71012653542365767</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.73382425458812039</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.69100650928419927</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.65068712690770769</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.61272033104578572</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0.57696885116048546</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0.54330342628140238</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0.54330342628140238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.66574362695967904</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.66574362695967904</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.68796023867636291</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.64781860245393685</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.61001918147597589</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.5744253103554241</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0.54090829796295503</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0.5093469621388147</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0.5093469621388147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="1">
-        <v>2.1292860867575243</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2.1292860867575243</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2.1292860867575243</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2.0050448549204294</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.8880529465934046</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1.7778873726401037</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1.6741498248215343</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1.5764652356959723</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1.5764652356959723</v>
       </c>
     </row>
   </sheetData>
@@ -16867,21 +16799,21 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" customWidth="1"/>
-    <col min="2" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="5.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -16892,16 +16824,37 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1971</v>
       </c>
       <c r="F2">
+        <v>2005</v>
+      </c>
+      <c r="G2">
+        <v>2020</v>
+      </c>
+      <c r="H2">
+        <v>2035</v>
+      </c>
+      <c r="I2">
+        <v>2050</v>
+      </c>
+      <c r="J2">
+        <v>2065</v>
+      </c>
+      <c r="K2">
+        <v>2080</v>
+      </c>
+      <c r="L2">
+        <v>2095</v>
+      </c>
+      <c r="M2">
         <v>2100</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -16912,16 +16865,37 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>57</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.7094391110222915</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.7094391110222915</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.7094391110222915</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.6096954353251778</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.5157716807808108</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.4273282621273939</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.3440454084866928</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1.2656220072190574</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1.2656220072190574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>158</v>
       </c>
@@ -16932,16 +16906,37 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>57</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.71012653542365767</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.71012653542365767</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.73382425458812039</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.69100650928419927</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.65068712690770769</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.61272033104578572</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.57696885116048546</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.54330342628140238</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.54330342628140238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>158</v>
       </c>
@@ -16952,16 +16947,37 @@
         <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>57</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.66574362695967904</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.66574362695967904</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.68796023867636291</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.64781860245393685</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.61001918147597589</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.5744253103554241</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.54090829796295503</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.5093469621388147</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.5093469621388147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>158</v>
       </c>
@@ -16972,13 +16988,34 @@
         <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1.25</v>
+        <v>57</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.1292860867575243</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2.1292860867575243</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2.1292860867575243</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2.0050448549204294</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.8880529465934046</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.7778873726401037</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.6741498248215343</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1.5764652356959723</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1.5764652356959723</v>
       </c>
     </row>
   </sheetData>
@@ -16994,20 +17031,21 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -17017,14 +17055,17 @@
       <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>1971</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>2100</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -17034,14 +17075,17 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>158</v>
       </c>
@@ -17051,14 +17095,17 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>158</v>
       </c>
@@ -17068,14 +17115,17 @@
       <c r="C5" t="s">
         <v>102</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>158</v>
       </c>
@@ -17085,11 +17135,14 @@
       <c r="C6" t="s">
         <v>103</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -17109,15 +17162,13 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -17125,84 +17176,84 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1971</v>
+      </c>
+      <c r="E2">
+        <v>2100</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
+        <v>102</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
+        <v>103</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17217,6 +17268,119 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -17390,7 +17554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -17560,7 +17724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -17943,7 +18107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -18581,7 +18745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -19217,7 +19381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -19502,149 +19666,6 @@
       </c>
       <c r="E17">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1971</v>
-      </c>
-      <c r="E2">
-        <v>2020</v>
-      </c>
-      <c r="F2">
-        <v>2035</v>
-      </c>
-      <c r="G2">
-        <v>2050</v>
-      </c>
-      <c r="H2">
-        <v>2065</v>
-      </c>
-      <c r="I2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3">
-        <v>0.91</v>
-      </c>
-      <c r="E3">
-        <v>0.91</v>
-      </c>
-      <c r="F3">
-        <v>0.92</v>
-      </c>
-      <c r="G3">
-        <v>0.93</v>
-      </c>
-      <c r="H3">
-        <v>0.94</v>
-      </c>
-      <c r="I3">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4">
-        <v>0.91</v>
-      </c>
-      <c r="E4">
-        <v>0.91</v>
-      </c>
-      <c r="F4">
-        <v>0.92</v>
-      </c>
-      <c r="G4">
-        <v>0.93</v>
-      </c>
-      <c r="H4">
-        <v>0.94</v>
-      </c>
-      <c r="I4">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5">
-        <v>0.91</v>
-      </c>
-      <c r="E5">
-        <v>0.91</v>
-      </c>
-      <c r="F5">
-        <v>0.92</v>
-      </c>
-      <c r="G5">
-        <v>0.93</v>
-      </c>
-      <c r="H5">
-        <v>0.94</v>
-      </c>
-      <c r="I5">
-        <v>0.94</v>
       </c>
     </row>
   </sheetData>
@@ -19927,6 +19948,149 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1971</v>
+      </c>
+      <c r="E2">
+        <v>2020</v>
+      </c>
+      <c r="F2">
+        <v>2035</v>
+      </c>
+      <c r="G2">
+        <v>2050</v>
+      </c>
+      <c r="H2">
+        <v>2065</v>
+      </c>
+      <c r="I2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3">
+        <v>0.91</v>
+      </c>
+      <c r="E3">
+        <v>0.91</v>
+      </c>
+      <c r="F3">
+        <v>0.92</v>
+      </c>
+      <c r="G3">
+        <v>0.93</v>
+      </c>
+      <c r="H3">
+        <v>0.94</v>
+      </c>
+      <c r="I3">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4">
+        <v>0.91</v>
+      </c>
+      <c r="E4">
+        <v>0.91</v>
+      </c>
+      <c r="F4">
+        <v>0.92</v>
+      </c>
+      <c r="G4">
+        <v>0.93</v>
+      </c>
+      <c r="H4">
+        <v>0.94</v>
+      </c>
+      <c r="I4">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5">
+        <v>0.91</v>
+      </c>
+      <c r="E5">
+        <v>0.91</v>
+      </c>
+      <c r="F5">
+        <v>0.92</v>
+      </c>
+      <c r="G5">
+        <v>0.93</v>
+      </c>
+      <c r="H5">
+        <v>0.94</v>
+      </c>
+      <c r="I5">
+        <v>0.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
@@ -20191,7 +20355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -20376,7 +20540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -20606,7 +20770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -20878,7 +21042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -21269,7 +21433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -21623,7 +21787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
@@ -22166,14 +22330,14 @@
       <c r="D10" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="3">
-        <v>111.78730206783794</v>
-      </c>
-      <c r="F10" s="3">
-        <v>111.78730206783794</v>
-      </c>
-      <c r="G10" s="3">
-        <v>111.78730206783794</v>
+      <c r="E10">
+        <v>111.79</v>
+      </c>
+      <c r="F10">
+        <v>111.79</v>
+      </c>
+      <c r="G10">
+        <v>111.79</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -22189,14 +22353,14 @@
       <c r="D11" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="3">
-        <v>582.47719635002909</v>
-      </c>
-      <c r="F11" s="3">
-        <v>582.47719635002909</v>
-      </c>
-      <c r="G11" s="3">
-        <v>582.47719635002909</v>
+      <c r="E11">
+        <v>582.48</v>
+      </c>
+      <c r="F11">
+        <v>582.48</v>
+      </c>
+      <c r="G11">
+        <v>582.48</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -22235,14 +22399,14 @@
       <c r="D13" t="s">
         <v>186</v>
       </c>
-      <c r="E13" s="3">
-        <v>142.57460317460317</v>
-      </c>
-      <c r="F13" s="3">
-        <v>142.57460317460317</v>
-      </c>
-      <c r="G13" s="3">
-        <v>142.57460317460317</v>
+      <c r="E13">
+        <v>142.57</v>
+      </c>
+      <c r="F13">
+        <v>142.57</v>
+      </c>
+      <c r="G13">
+        <v>142.57</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -22258,13 +22422,13 @@
       <c r="D14" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>128</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>128</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>128</v>
       </c>
     </row>

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="22720" yWindow="1240" windowWidth="24980" windowHeight="16240" tabRatio="684" firstSheet="14" activeTab="15"/>
+    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="15820" tabRatio="684" firstSheet="52" activeTab="54"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -21202,16 +21202,16 @@
         <v>57</v>
       </c>
       <c r="E7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -21358,16 +21358,16 @@
         <v>57</v>
       </c>
       <c r="E13">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="F13">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="G13">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -21384,16 +21384,16 @@
         <v>57</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">

--- a/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="15820" tabRatio="684" firstSheet="52" activeTab="54"/>
+    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="15820" tabRatio="684" firstSheet="10" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="A21.sector.csv" sheetId="5" r:id="rId1"/>
@@ -760,8 +760,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1709">
+  <cellStyleXfs count="1715">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2479,7 +2485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1709">
+  <cellStyles count="1715">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -3334,6 +3340,9 @@
     <cellStyle name="Followed Hyperlink" xfId="1704" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1706" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="1708" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1710" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1712" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="1714" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -4188,6 +4197,9 @@
     <cellStyle name="Hyperlink" xfId="1703" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1705" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1707" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1709" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1711" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1713" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5300,7 +5312,7 @@
         <v>43</v>
       </c>
       <c r="C9">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5314,7 +5326,7 @@
         <v>45</v>
       </c>
       <c r="C10">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -5328,7 +5340,7 @@
         <v>46</v>
       </c>
       <c r="C11">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="E11">
         <v>0.1</v>
@@ -5520,7 +5532,7 @@
         <v>49</v>
       </c>
       <c r="E9">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="G9" t="s">
         <v>42</v>
@@ -5540,7 +5552,7 @@
         <v>49</v>
       </c>
       <c r="E10">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="G10" t="s">
         <v>42</v>
@@ -5560,7 +5572,7 @@
         <v>49</v>
       </c>
       <c r="E11">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="G11" t="s">
         <v>42</v>
